--- a/research/traditional_assets/database/data/qatar/qatar_education.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_education.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0833050126906406</v>
+        <v>0.08326220767794995</v>
       </c>
       <c r="C2">
-        <v>59.86297392398641</v>
+        <v>59.3014108568792</v>
       </c>
       <c r="D2">
-        <v>59.28997392398641</v>
+        <v>59.3174108568792</v>
       </c>
       <c r="E2">
-        <v>-13.1</v>
+        <v>-12.511</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.589</v>
       </c>
       <c r="G2">
         <v>0.573</v>
@@ -1433,28 +1433,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0296267</v>
       </c>
       <c r="N2">
-        <v>2.036938775510204</v>
+        <v>2.007312075510204</v>
       </c>
       <c r="O2">
-        <v>0.2036938775510204</v>
+        <v>0.2007312075510204</v>
       </c>
       <c r="P2">
-        <v>1.833244897959184</v>
+        <v>1.806580867959184</v>
       </c>
       <c r="Q2">
-        <v>5.643244897959184</v>
+        <v>5.616580867959184</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0833050126906406</v>
+        <v>0.0836459673514646</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129921</v>
+        <v>0.7585717011022011</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>68.75348167396992</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08326220767794995</v>
+        <v>0.08321940266525932</v>
       </c>
       <c r="C3">
-        <v>59.3014108568792</v>
+        <v>58.73987319487021</v>
       </c>
       <c r="D3">
-        <v>59.3174108568792</v>
+        <v>59.3448731948702</v>
       </c>
       <c r="E3">
-        <v>-12.511</v>
+        <v>-11.922</v>
       </c>
       <c r="F3">
-        <v>0.589</v>
+        <v>1.178</v>
       </c>
       <c r="G3">
         <v>0.573</v>
@@ -1515,28 +1515,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M3">
-        <v>0.0296267</v>
+        <v>0.05925339999999999</v>
       </c>
       <c r="N3">
-        <v>2.007312075510204</v>
+        <v>1.977685375510204</v>
       </c>
       <c r="O3">
-        <v>0.2007312075510204</v>
+        <v>0.1977685375510204</v>
       </c>
       <c r="P3">
-        <v>1.806580867959184</v>
+        <v>1.779916837959184</v>
       </c>
       <c r="Q3">
-        <v>5.616580867959184</v>
+        <v>5.589916837959183</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0836459673514646</v>
+        <v>0.08399388027067277</v>
       </c>
       <c r="T3">
-        <v>0.7585717011022011</v>
+        <v>0.7655451493564961</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>68.75348167396992</v>
+        <v>34.37674083698496</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08321940266525932</v>
+        <v>0.08317659765256867</v>
       </c>
       <c r="C4">
-        <v>58.73987319487021</v>
+        <v>58.17836097326138</v>
       </c>
       <c r="D4">
-        <v>59.3448731948702</v>
+        <v>59.37236097326138</v>
       </c>
       <c r="E4">
-        <v>-11.922</v>
+        <v>-11.333</v>
       </c>
       <c r="F4">
-        <v>1.178</v>
+        <v>1.767</v>
       </c>
       <c r="G4">
         <v>0.573</v>
@@ -1597,28 +1597,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M4">
-        <v>0.05925339999999999</v>
+        <v>0.08888009999999999</v>
       </c>
       <c r="N4">
-        <v>1.977685375510204</v>
+        <v>1.948058675510204</v>
       </c>
       <c r="O4">
-        <v>0.1977685375510204</v>
+        <v>0.1948058675510204</v>
       </c>
       <c r="P4">
-        <v>1.779916837959184</v>
+        <v>1.753252807959184</v>
       </c>
       <c r="Q4">
-        <v>5.589916837959183</v>
+        <v>5.563252807959184</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08399388027067277</v>
+        <v>0.08434896665213265</v>
       </c>
       <c r="T4">
-        <v>0.7655451493564961</v>
+        <v>0.7726623800490238</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>34.37674083698496</v>
+        <v>22.91782722465664</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08317659765256867</v>
+        <v>0.08313379263987804</v>
       </c>
       <c r="C5">
-        <v>58.17836097326138</v>
+        <v>57.61687422742008</v>
       </c>
       <c r="D5">
-        <v>59.37236097326138</v>
+        <v>59.39987422742009</v>
       </c>
       <c r="E5">
-        <v>-11.333</v>
+        <v>-10.744</v>
       </c>
       <c r="F5">
-        <v>1.767</v>
+        <v>2.356</v>
       </c>
       <c r="G5">
         <v>0.573</v>
@@ -1679,28 +1679,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M5">
-        <v>0.08888009999999999</v>
+        <v>0.1185068</v>
       </c>
       <c r="N5">
-        <v>1.948058675510204</v>
+        <v>1.918431975510204</v>
       </c>
       <c r="O5">
-        <v>0.1948058675510204</v>
+        <v>0.1918431975510204</v>
       </c>
       <c r="P5">
-        <v>1.753252807959184</v>
+        <v>1.726588777959184</v>
       </c>
       <c r="Q5">
-        <v>5.563252807959184</v>
+        <v>5.536588777959183</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08434896665213265</v>
+        <v>0.08471145066653962</v>
       </c>
       <c r="T5">
-        <v>0.7726623800490238</v>
+        <v>0.7799278863809794</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.91782722465664</v>
+        <v>17.18837041849248</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08313379263987804</v>
+        <v>0.08309098762718738</v>
       </c>
       <c r="C6">
-        <v>57.61687422742008</v>
+        <v>57.05541299277931</v>
       </c>
       <c r="D6">
-        <v>59.39987422742009</v>
+        <v>59.42741299277931</v>
       </c>
       <c r="E6">
-        <v>-10.744</v>
+        <v>-10.155</v>
       </c>
       <c r="F6">
-        <v>2.356</v>
+        <v>2.945</v>
       </c>
       <c r="G6">
         <v>0.573</v>
@@ -1761,28 +1761,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M6">
-        <v>0.1185068</v>
+        <v>0.1481335</v>
       </c>
       <c r="N6">
-        <v>1.918431975510204</v>
+        <v>1.888805275510204</v>
       </c>
       <c r="O6">
-        <v>0.1918431975510204</v>
+        <v>0.1888805275510204</v>
       </c>
       <c r="P6">
-        <v>1.726588777959184</v>
+        <v>1.699924747959184</v>
       </c>
       <c r="Q6">
-        <v>5.536588777959183</v>
+        <v>5.509924747959184</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08471145066653962</v>
+        <v>0.08508156592335514</v>
       </c>
       <c r="T6">
-        <v>0.7799278863809794</v>
+        <v>0.7873463507409759</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.18837041849248</v>
+        <v>13.75069633479398</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08309098762718738</v>
+        <v>0.08312918261449675</v>
       </c>
       <c r="C7">
-        <v>57.05541299277931</v>
+        <v>56.44183887809468</v>
       </c>
       <c r="D7">
-        <v>59.42741299277931</v>
+        <v>59.40283887809468</v>
       </c>
       <c r="E7">
-        <v>-10.155</v>
+        <v>-9.565999999999999</v>
       </c>
       <c r="F7">
-        <v>2.945</v>
+        <v>3.534</v>
       </c>
       <c r="G7">
         <v>0.573</v>
@@ -1843,45 +1843,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M7">
-        <v>0.1481335</v>
+        <v>0.1830612</v>
       </c>
       <c r="N7">
-        <v>1.888805275510204</v>
+        <v>1.853877575510204</v>
       </c>
       <c r="O7">
-        <v>0.1888805275510204</v>
+        <v>0.1853877575510204</v>
       </c>
       <c r="P7">
-        <v>1.699924747959184</v>
+        <v>1.668489817959184</v>
       </c>
       <c r="Q7">
-        <v>5.509924747959184</v>
+        <v>5.478489817959184</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08508156592335514</v>
+        <v>0.08545955597286889</v>
       </c>
       <c r="T7">
-        <v>0.7873463507409759</v>
+        <v>0.7949226547682066</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.1</v>
       </c>
       <c r="W7">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.75069633479398</v>
+        <v>11.1270917895775</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08312918261449675</v>
+        <v>0.08320697760180611</v>
       </c>
       <c r="C8">
-        <v>56.44183887809468</v>
+        <v>55.80284948386278</v>
       </c>
       <c r="D8">
-        <v>59.40283887809468</v>
+        <v>59.35284948386278</v>
       </c>
       <c r="E8">
-        <v>-9.565999999999999</v>
+        <v>-8.977</v>
       </c>
       <c r="F8">
-        <v>3.534</v>
+        <v>4.122999999999999</v>
       </c>
       <c r="G8">
         <v>0.573</v>
@@ -1925,45 +1925,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M8">
-        <v>0.1830612</v>
+        <v>0.2205805</v>
       </c>
       <c r="N8">
-        <v>1.853877575510204</v>
+        <v>1.816358275510204</v>
       </c>
       <c r="O8">
-        <v>0.1853877575510204</v>
+        <v>0.1816358275510204</v>
       </c>
       <c r="P8">
-        <v>1.668489817959184</v>
+        <v>1.634722447959184</v>
       </c>
       <c r="Q8">
-        <v>5.478489817959184</v>
+        <v>5.444722447959184</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08545955597286889</v>
+        <v>0.08584567484065173</v>
       </c>
       <c r="T8">
-        <v>0.7949226547682066</v>
+        <v>0.8026618900648399</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.1</v>
       </c>
       <c r="W8">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>11.1270917895775</v>
+        <v>9.234446270228803</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08320697760180611</v>
+        <v>0.08319297258911547</v>
       </c>
       <c r="C9">
-        <v>55.80284948386278</v>
+        <v>55.22284259455346</v>
       </c>
       <c r="D9">
-        <v>59.35284948386278</v>
+        <v>59.36184259455345</v>
       </c>
       <c r="E9">
-        <v>-8.977</v>
+        <v>-8.388</v>
       </c>
       <c r="F9">
-        <v>4.123</v>
+        <v>4.712</v>
       </c>
       <c r="G9">
         <v>0.573</v>
@@ -2007,28 +2007,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M9">
-        <v>0.2205805</v>
+        <v>0.252092</v>
       </c>
       <c r="N9">
-        <v>1.816358275510204</v>
+        <v>1.784846775510204</v>
       </c>
       <c r="O9">
-        <v>0.1816358275510204</v>
+        <v>0.1784846775510204</v>
       </c>
       <c r="P9">
-        <v>1.634722447959184</v>
+        <v>1.606362097959184</v>
       </c>
       <c r="Q9">
-        <v>5.444722447959184</v>
+        <v>5.416362097959183</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08584567484065174</v>
+        <v>0.08624018759686464</v>
       </c>
       <c r="T9">
-        <v>0.8026618900648401</v>
+        <v>0.8105693696070524</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.234446270228801</v>
+        <v>8.080140486450201</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08319297258911547</v>
+        <v>0.08324376757642482</v>
       </c>
       <c r="C10">
-        <v>55.22284259455346</v>
+        <v>54.60123832407574</v>
       </c>
       <c r="D10">
-        <v>59.36184259455345</v>
+        <v>59.32923832407574</v>
       </c>
       <c r="E10">
-        <v>-8.388</v>
+        <v>-7.799</v>
       </c>
       <c r="F10">
-        <v>4.712</v>
+        <v>5.300999999999999</v>
       </c>
       <c r="G10">
         <v>0.573</v>
@@ -2089,45 +2089,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M10">
-        <v>0.252092</v>
+        <v>0.2878442999999999</v>
       </c>
       <c r="N10">
-        <v>1.784846775510204</v>
+        <v>1.749094475510204</v>
       </c>
       <c r="O10">
-        <v>0.1784846775510204</v>
+        <v>0.1749094475510204</v>
       </c>
       <c r="P10">
-        <v>1.606362097959184</v>
+        <v>1.574185027959184</v>
       </c>
       <c r="Q10">
-        <v>5.416362097959183</v>
+        <v>5.384185027959184</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08624018759686464</v>
+        <v>0.0866433709631042</v>
       </c>
       <c r="T10">
-        <v>0.8105693696070524</v>
+        <v>0.8186506399084342</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.1</v>
       </c>
       <c r="W10">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.080140486450201</v>
+        <v>7.076529830572308</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08324376757642482</v>
+        <v>0.0832369625637342</v>
       </c>
       <c r="C11">
-        <v>54.60123832407574</v>
+        <v>54.01660424562978</v>
       </c>
       <c r="D11">
-        <v>59.32923832407574</v>
+        <v>59.33360424562978</v>
       </c>
       <c r="E11">
-        <v>-7.799</v>
+        <v>-7.21</v>
       </c>
       <c r="F11">
-        <v>5.300999999999999</v>
+        <v>5.89</v>
       </c>
       <c r="G11">
         <v>0.573</v>
@@ -2171,28 +2171,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M11">
-        <v>0.2878442999999999</v>
+        <v>0.319827</v>
       </c>
       <c r="N11">
-        <v>1.749094475510204</v>
+        <v>1.717111775510204</v>
       </c>
       <c r="O11">
-        <v>0.1749094475510204</v>
+        <v>0.1717111775510204</v>
       </c>
       <c r="P11">
-        <v>1.574185027959184</v>
+        <v>1.545400597959184</v>
       </c>
       <c r="Q11">
-        <v>5.384185027959184</v>
+        <v>5.355400597959184</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0866433709631042</v>
+        <v>0.08705551395970465</v>
       </c>
       <c r="T11">
-        <v>0.8186506399084342</v>
+        <v>0.8269114939942914</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.076529830572308</v>
+        <v>6.368876847515076</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0832369625637342</v>
+        <v>0.08332915755104355</v>
       </c>
       <c r="C12">
-        <v>54.01660424562978</v>
+        <v>53.36850887116549</v>
       </c>
       <c r="D12">
-        <v>59.33360424562978</v>
+        <v>59.27450887116549</v>
       </c>
       <c r="E12">
-        <v>-7.209999999999999</v>
+        <v>-6.621</v>
       </c>
       <c r="F12">
-        <v>5.890000000000001</v>
+        <v>6.479</v>
       </c>
       <c r="G12">
         <v>0.573</v>
@@ -2253,45 +2253,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M12">
-        <v>0.319827</v>
+        <v>0.3582887</v>
       </c>
       <c r="N12">
-        <v>1.717111775510204</v>
+        <v>1.678650075510204</v>
       </c>
       <c r="O12">
-        <v>0.1717111775510204</v>
+        <v>0.1678650075510204</v>
       </c>
       <c r="P12">
-        <v>1.545400597959184</v>
+        <v>1.510785067959184</v>
       </c>
       <c r="Q12">
-        <v>5.355400597959184</v>
+        <v>5.320785067959184</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08705551395970465</v>
+        <v>0.08747691859667814</v>
       </c>
       <c r="T12">
-        <v>0.8269114939942914</v>
+        <v>0.835357985250617</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.368876847515075</v>
+        <v>5.685188440244429</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08332915755104355</v>
+        <v>0.08333135253835292</v>
       </c>
       <c r="C13">
-        <v>53.36850887116549</v>
+        <v>52.77810335731608</v>
       </c>
       <c r="D13">
-        <v>59.27450887116549</v>
+        <v>59.27310335731608</v>
       </c>
       <c r="E13">
-        <v>-6.621</v>
+        <v>-6.032</v>
       </c>
       <c r="F13">
-        <v>6.479</v>
+        <v>7.068</v>
       </c>
       <c r="G13">
         <v>0.573</v>
@@ -2335,28 +2335,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M13">
-        <v>0.3582887</v>
+        <v>0.3908604</v>
       </c>
       <c r="N13">
-        <v>1.678650075510204</v>
+        <v>1.646078375510204</v>
       </c>
       <c r="O13">
-        <v>0.1678650075510204</v>
+        <v>0.1646078375510204</v>
       </c>
       <c r="P13">
-        <v>1.510785067959184</v>
+        <v>1.481470537959184</v>
       </c>
       <c r="Q13">
-        <v>5.320785067959184</v>
+        <v>5.291470537959183</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08747691859667814</v>
+        <v>0.08790790061176468</v>
       </c>
       <c r="T13">
-        <v>0.835357985250617</v>
+        <v>0.843996442217314</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.685188440244429</v>
+        <v>5.211422736890727</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08333135253835292</v>
+        <v>0.08333354752566227</v>
       </c>
       <c r="C14">
-        <v>52.77810335731608</v>
+        <v>52.18769791012005</v>
       </c>
       <c r="D14">
-        <v>59.27310335731608</v>
+        <v>59.27169791012005</v>
       </c>
       <c r="E14">
-        <v>-6.032</v>
+        <v>-5.443</v>
       </c>
       <c r="F14">
-        <v>7.068</v>
+        <v>7.657</v>
       </c>
       <c r="G14">
         <v>0.573</v>
@@ -2417,28 +2417,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M14">
-        <v>0.3908604</v>
+        <v>0.4234321</v>
       </c>
       <c r="N14">
-        <v>1.646078375510204</v>
+        <v>1.613506675510204</v>
       </c>
       <c r="O14">
-        <v>0.1646078375510204</v>
+        <v>0.1613506675510204</v>
       </c>
       <c r="P14">
-        <v>1.481470537959184</v>
+        <v>1.452156007959184</v>
       </c>
       <c r="Q14">
-        <v>5.291470537959183</v>
+        <v>5.262156007959184</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08790790061176468</v>
+        <v>0.08834879025938192</v>
       </c>
       <c r="T14">
-        <v>0.843996442217314</v>
+        <v>0.8528334844016359</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.211422736890727</v>
+        <v>4.810544064822208</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08333354752566227</v>
+        <v>0.08365074251297164</v>
       </c>
       <c r="C15">
-        <v>52.18769791012005</v>
+        <v>51.39629676300723</v>
       </c>
       <c r="D15">
-        <v>59.27169791012005</v>
+        <v>59.06929676300723</v>
       </c>
       <c r="E15">
-        <v>-5.443</v>
+        <v>-4.853999999999999</v>
       </c>
       <c r="F15">
-        <v>7.657</v>
+        <v>8.246</v>
       </c>
       <c r="G15">
         <v>0.573</v>
@@ -2499,45 +2499,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M15">
-        <v>0.4234321</v>
+        <v>0.4766188000000001</v>
       </c>
       <c r="N15">
-        <v>1.613506675510204</v>
+        <v>1.560319975510204</v>
       </c>
       <c r="O15">
-        <v>0.1613506675510204</v>
+        <v>0.1560319975510204</v>
       </c>
       <c r="P15">
-        <v>1.452156007959184</v>
+        <v>1.404287977959184</v>
       </c>
       <c r="Q15">
-        <v>5.262156007959184</v>
+        <v>5.214287977959184</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08834879025938192</v>
+        <v>0.08879993315461818</v>
       </c>
       <c r="T15">
-        <v>0.8528334844016359</v>
+        <v>0.8618760391948956</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.810544064822208</v>
+        <v>4.273727296342914</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08365074251297164</v>
+        <v>0.08414793750028099</v>
       </c>
       <c r="C16">
-        <v>51.39629676300723</v>
+        <v>50.49280489819768</v>
       </c>
       <c r="D16">
-        <v>59.06929676300723</v>
+        <v>58.75480489819768</v>
       </c>
       <c r="E16">
-        <v>-4.853999999999999</v>
+        <v>-4.264999999999999</v>
       </c>
       <c r="F16">
-        <v>8.246</v>
+        <v>8.835000000000001</v>
       </c>
       <c r="G16">
         <v>0.573</v>
@@ -2581,45 +2581,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M16">
-        <v>0.4766188000000001</v>
+        <v>0.5415855000000001</v>
       </c>
       <c r="N16">
-        <v>1.560319975510204</v>
+        <v>1.495353275510204</v>
       </c>
       <c r="O16">
-        <v>0.1560319975510204</v>
+        <v>0.1495353275510204</v>
       </c>
       <c r="P16">
-        <v>1.404287977959184</v>
+        <v>1.345817947959184</v>
       </c>
       <c r="Q16">
-        <v>5.214287977959184</v>
+        <v>5.155817947959184</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08879993315461818</v>
+        <v>0.08926169117680116</v>
       </c>
       <c r="T16">
-        <v>0.8618760391948956</v>
+        <v>0.8711313599832909</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0.1</v>
       </c>
       <c r="W16">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.273727296342914</v>
+        <v>3.761065936052948</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08414793750028099</v>
+        <v>0.08420413248759034</v>
       </c>
       <c r="C17">
-        <v>50.49280489819768</v>
+        <v>49.86847026558099</v>
       </c>
       <c r="D17">
-        <v>58.75480489819768</v>
+        <v>58.71947026558099</v>
       </c>
       <c r="E17">
-        <v>-4.265000000000001</v>
+        <v>-3.676</v>
       </c>
       <c r="F17">
-        <v>8.834999999999999</v>
+        <v>9.423999999999999</v>
       </c>
       <c r="G17">
         <v>0.573</v>
@@ -2663,28 +2663,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M17">
-        <v>0.5415854999999999</v>
+        <v>0.5776912</v>
       </c>
       <c r="N17">
-        <v>1.495353275510204</v>
+        <v>1.459247575510204</v>
       </c>
       <c r="O17">
-        <v>0.1495353275510204</v>
+        <v>0.1459247575510204</v>
       </c>
       <c r="P17">
-        <v>1.345817947959184</v>
+        <v>1.313322817959184</v>
       </c>
       <c r="Q17">
-        <v>5.155817947959184</v>
+        <v>5.123322817959184</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08926169117680116</v>
+        <v>0.08973444343760756</v>
       </c>
       <c r="T17">
-        <v>0.8711313599832909</v>
+        <v>0.8806070455523622</v>
       </c>
       <c r="U17">
         <v>0.0613</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.761065936052949</v>
+        <v>3.52599931504964</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08420413248759034</v>
+        <v>0.08468872747489971</v>
       </c>
       <c r="C18">
-        <v>49.86847026558099</v>
+        <v>48.97651800436476</v>
       </c>
       <c r="D18">
-        <v>58.71947026558099</v>
+        <v>58.41651800436475</v>
       </c>
       <c r="E18">
-        <v>-3.676</v>
+        <v>-3.087</v>
       </c>
       <c r="F18">
-        <v>9.423999999999999</v>
+        <v>10.013</v>
       </c>
       <c r="G18">
         <v>0.573</v>
@@ -2745,45 +2745,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M18">
-        <v>0.5776912</v>
+        <v>0.6418333000000001</v>
       </c>
       <c r="N18">
-        <v>1.459247575510204</v>
+        <v>1.395105475510204</v>
       </c>
       <c r="O18">
-        <v>0.1459247575510204</v>
+        <v>0.1395105475510204</v>
       </c>
       <c r="P18">
-        <v>1.313322817959184</v>
+        <v>1.255594927959184</v>
       </c>
       <c r="Q18">
-        <v>5.123322817959184</v>
+        <v>5.065594927959184</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08973444343760756</v>
+        <v>0.09021858731915627</v>
       </c>
       <c r="T18">
-        <v>0.8806070455523622</v>
+        <v>0.8903110608941823</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.52599931504964</v>
+        <v>3.173625886207843</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08468872747489971</v>
+        <v>0.08603372246220906</v>
       </c>
       <c r="C19">
-        <v>48.97651800436476</v>
+        <v>47.56282060414581</v>
       </c>
       <c r="D19">
-        <v>58.41651800436475</v>
+        <v>57.59182060414581</v>
       </c>
       <c r="E19">
-        <v>-3.087</v>
+        <v>-2.497999999999999</v>
       </c>
       <c r="F19">
-        <v>10.013</v>
+        <v>10.602</v>
       </c>
       <c r="G19">
         <v>0.573</v>
@@ -2827,45 +2827,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M19">
-        <v>0.6418333000000001</v>
+        <v>0.7622838000000001</v>
       </c>
       <c r="N19">
-        <v>1.395105475510204</v>
+        <v>1.274654975510204</v>
       </c>
       <c r="O19">
-        <v>0.1395105475510204</v>
+        <v>0.1274654975510204</v>
       </c>
       <c r="P19">
-        <v>1.255594927959184</v>
+        <v>1.147189477959184</v>
       </c>
       <c r="Q19">
-        <v>5.065594927959184</v>
+        <v>4.957189477959184</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09021858731915627</v>
+        <v>0.09071453958805983</v>
       </c>
       <c r="T19">
-        <v>0.8903110608941823</v>
+        <v>0.9002517595370223</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.173625886207843</v>
+        <v>2.672152780250878</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08603372246220907</v>
+        <v>0.08618531744951843</v>
       </c>
       <c r="C20">
-        <v>47.56282060414581</v>
+        <v>46.88232642940912</v>
       </c>
       <c r="D20">
-        <v>57.5918206041458</v>
+        <v>57.50032642940912</v>
       </c>
       <c r="E20">
-        <v>-2.498000000000001</v>
+        <v>-1.908999999999999</v>
       </c>
       <c r="F20">
-        <v>10.602</v>
+        <v>11.191</v>
       </c>
       <c r="G20">
         <v>0.573</v>
@@ -2909,28 +2909,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M20">
-        <v>0.7622838</v>
+        <v>0.8046329000000001</v>
       </c>
       <c r="N20">
-        <v>1.274654975510204</v>
+        <v>1.232305875510204</v>
       </c>
       <c r="O20">
-        <v>0.1274654975510204</v>
+        <v>0.1232305875510204</v>
       </c>
       <c r="P20">
-        <v>1.147189477959184</v>
+        <v>1.109075287959184</v>
       </c>
       <c r="Q20">
-        <v>4.957189477959184</v>
+        <v>4.919075287959184</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09071453958805983</v>
+        <v>0.09122273759199806</v>
       </c>
       <c r="T20">
-        <v>0.9002517595370223</v>
+        <v>0.9104379075290682</v>
       </c>
       <c r="U20">
         <v>0.07190000000000001</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.672152780250878</v>
+        <v>2.531513160237673</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08618531744951843</v>
+        <v>0.08703891243682779</v>
       </c>
       <c r="C21">
-        <v>46.88232642940912</v>
+        <v>45.78352353354889</v>
       </c>
       <c r="D21">
-        <v>57.50032642940912</v>
+        <v>56.99052353354889</v>
       </c>
       <c r="E21">
-        <v>-1.908999999999999</v>
+        <v>-1.319999999999999</v>
       </c>
       <c r="F21">
-        <v>11.191</v>
+        <v>11.78</v>
       </c>
       <c r="G21">
         <v>0.573</v>
@@ -2991,45 +2991,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M21">
-        <v>0.8046329000000001</v>
+        <v>0.8929240000000002</v>
       </c>
       <c r="N21">
-        <v>1.232305875510204</v>
+        <v>1.144014775510204</v>
       </c>
       <c r="O21">
-        <v>0.1232305875510204</v>
+        <v>0.1144014775510204</v>
       </c>
       <c r="P21">
-        <v>1.109075287959184</v>
+        <v>1.029613297959183</v>
       </c>
       <c r="Q21">
-        <v>4.919075287959184</v>
+        <v>4.839613297959183</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09122273759199806</v>
+        <v>0.09174364054603473</v>
       </c>
       <c r="T21">
-        <v>0.9104379075290682</v>
+        <v>0.9208787092209154</v>
       </c>
       <c r="U21">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.531513160237673</v>
+        <v>2.281200612269581</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08703891243682779</v>
+        <v>0.08722560742413715</v>
       </c>
       <c r="C22">
-        <v>45.78352353354889</v>
+        <v>45.08422389569375</v>
       </c>
       <c r="D22">
-        <v>56.99052353354889</v>
+        <v>56.88022389569375</v>
       </c>
       <c r="E22">
-        <v>-1.319999999999999</v>
+        <v>-0.7309999999999981</v>
       </c>
       <c r="F22">
-        <v>11.78</v>
+        <v>12.369</v>
       </c>
       <c r="G22">
         <v>0.573</v>
@@ -3073,28 +3073,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M22">
-        <v>0.8929240000000002</v>
+        <v>0.9375702000000002</v>
       </c>
       <c r="N22">
-        <v>1.144014775510204</v>
+        <v>1.099368575510204</v>
       </c>
       <c r="O22">
-        <v>0.1144014775510204</v>
+        <v>0.1099368575510204</v>
       </c>
       <c r="P22">
-        <v>1.029613297959183</v>
+        <v>0.9894317179591836</v>
       </c>
       <c r="Q22">
-        <v>4.839613297959183</v>
+        <v>4.799431717959184</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09174364054603473</v>
+        <v>0.0922777309166293</v>
       </c>
       <c r="T22">
-        <v>0.9208787092209154</v>
+        <v>0.9315838350062269</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.281200612269581</v>
+        <v>2.172572011685316</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08722560742413715</v>
+        <v>0.08741230241144651</v>
       </c>
       <c r="C23">
-        <v>45.08422389569375</v>
+        <v>44.38535038164682</v>
       </c>
       <c r="D23">
-        <v>56.88022389569375</v>
+        <v>56.77035038164682</v>
       </c>
       <c r="E23">
-        <v>-0.7309999999999999</v>
+        <v>-0.1419999999999995</v>
       </c>
       <c r="F23">
-        <v>12.369</v>
+        <v>12.958</v>
       </c>
       <c r="G23">
         <v>0.573</v>
@@ -3155,28 +3155,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M23">
-        <v>0.9375702</v>
+        <v>0.9822164000000001</v>
       </c>
       <c r="N23">
-        <v>1.099368575510204</v>
+        <v>1.054722375510204</v>
       </c>
       <c r="O23">
-        <v>0.1099368575510204</v>
+        <v>0.1054722375510204</v>
       </c>
       <c r="P23">
-        <v>0.9894317179591836</v>
+        <v>0.9492501379591838</v>
       </c>
       <c r="Q23">
-        <v>4.799431717959184</v>
+        <v>4.759250137959183</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0922777309166293</v>
+        <v>0.09282551591211091</v>
       </c>
       <c r="T23">
-        <v>0.9315838350062269</v>
+        <v>0.9425634511962901</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.172572011685316</v>
+        <v>2.073818738426893</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08741230241144651</v>
+        <v>0.09053839739875588</v>
       </c>
       <c r="C24">
-        <v>44.38535038164682</v>
+        <v>42.0176691125691</v>
       </c>
       <c r="D24">
-        <v>56.77035038164682</v>
+        <v>54.99166911256909</v>
       </c>
       <c r="E24">
-        <v>-0.1419999999999995</v>
+        <v>0.447000000000001</v>
       </c>
       <c r="F24">
-        <v>12.958</v>
+        <v>13.547</v>
       </c>
       <c r="G24">
         <v>0.573</v>
@@ -3237,45 +3237,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M24">
-        <v>0.9822164000000001</v>
+        <v>1.21923</v>
       </c>
       <c r="N24">
-        <v>1.054722375510204</v>
+        <v>0.8177087755102042</v>
       </c>
       <c r="O24">
-        <v>0.1054722375510204</v>
+        <v>0.08177087755102042</v>
       </c>
       <c r="P24">
-        <v>0.9492501379591838</v>
+        <v>0.7359378979591837</v>
       </c>
       <c r="Q24">
-        <v>4.759250137959183</v>
+        <v>4.545937897959184</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09282551591211091</v>
+        <v>0.09338752908929333</v>
       </c>
       <c r="T24">
-        <v>0.9425634511962901</v>
+        <v>0.9538282522224589</v>
       </c>
       <c r="U24">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.073818738426893</v>
+        <v>1.670676390435114</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09053839739875588</v>
+        <v>0.09085289238606523</v>
       </c>
       <c r="C25">
-        <v>42.0176691125691</v>
+        <v>41.25587924694612</v>
       </c>
       <c r="D25">
-        <v>54.99166911256909</v>
+        <v>54.81887924694612</v>
       </c>
       <c r="E25">
-        <v>0.447000000000001</v>
+        <v>1.036000000000001</v>
       </c>
       <c r="F25">
-        <v>13.547</v>
+        <v>14.136</v>
       </c>
       <c r="G25">
         <v>0.573</v>
@@ -3319,28 +3319,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M25">
-        <v>1.21923</v>
+        <v>1.27224</v>
       </c>
       <c r="N25">
-        <v>0.8177087755102042</v>
+        <v>0.7646987755102042</v>
       </c>
       <c r="O25">
-        <v>0.08177087755102042</v>
+        <v>0.07646987755102042</v>
       </c>
       <c r="P25">
-        <v>0.7359378979591837</v>
+        <v>0.6882288979591837</v>
       </c>
       <c r="Q25">
-        <v>4.545937897959184</v>
+        <v>4.498228897959184</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09338752908929333</v>
+        <v>0.09396433208692792</v>
       </c>
       <c r="T25">
-        <v>0.9538282522224589</v>
+        <v>0.9653894953808951</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.670676390435114</v>
+        <v>1.601064874166984</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09085289238606523</v>
+        <v>0.09116738737337458</v>
       </c>
       <c r="C26">
-        <v>41.25587924694612</v>
+        <v>40.4951718296319</v>
       </c>
       <c r="D26">
-        <v>54.81887924694612</v>
+        <v>54.6471718296319</v>
       </c>
       <c r="E26">
-        <v>1.036</v>
+        <v>1.625</v>
       </c>
       <c r="F26">
-        <v>14.136</v>
+        <v>14.725</v>
       </c>
       <c r="G26">
         <v>0.573</v>
@@ -3401,28 +3401,28 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M26">
-        <v>1.27224</v>
+        <v>1.32525</v>
       </c>
       <c r="N26">
-        <v>0.7646987755102044</v>
+        <v>0.7116887755102044</v>
       </c>
       <c r="O26">
-        <v>0.07646987755102044</v>
+        <v>0.07116887755102044</v>
       </c>
       <c r="P26">
-        <v>0.688228897959184</v>
+        <v>0.640519897959184</v>
       </c>
       <c r="Q26">
-        <v>4.498228897959184</v>
+        <v>4.450519897959184</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09396433208692792</v>
+        <v>0.09455651649783278</v>
       </c>
       <c r="T26">
-        <v>0.9653894953808951</v>
+        <v>0.9772590383568899</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.601064874166985</v>
+        <v>1.537022279200305</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09116738737337458</v>
+        <v>0.1052231731196864</v>
       </c>
       <c r="C27">
-        <v>40.4951718296319</v>
+        <v>33.19549152855567</v>
       </c>
       <c r="D27">
-        <v>54.6471718296319</v>
+        <v>47.93649152855567</v>
       </c>
       <c r="E27">
-        <v>1.625</v>
+        <v>2.214</v>
       </c>
       <c r="F27">
-        <v>14.725</v>
+        <v>15.314</v>
       </c>
       <c r="G27">
         <v>0.573</v>
@@ -3483,45 +3483,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M27">
-        <v>1.32525</v>
+        <v>2.2480952</v>
       </c>
       <c r="N27">
-        <v>0.7116887755102044</v>
+        <v>-0.2111564244897961</v>
       </c>
       <c r="O27">
-        <v>0.07116887755102044</v>
+        <v>-0.02111564244897961</v>
       </c>
       <c r="P27">
-        <v>0.640519897959184</v>
+        <v>-0.1900407820408165</v>
       </c>
       <c r="Q27">
-        <v>4.450519897959184</v>
+        <v>3.619959217959184</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09455651649783278</v>
+        <v>0.09528847736200963</v>
       </c>
       <c r="T27">
-        <v>0.9772590383568899</v>
+        <v>0.9919302130350918</v>
       </c>
       <c r="U27">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.1</v>
+        <v>0.09060731838714856</v>
       </c>
       <c r="W27">
-        <v>0.081</v>
+        <v>0.1334988456607666</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.537022279200305</v>
+        <v>0.9060731838714855</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1052231731196864</v>
+        <v>0.1062331731196864</v>
       </c>
       <c r="C28">
-        <v>33.19549152855567</v>
+        <v>32.18720013640395</v>
       </c>
       <c r="D28">
-        <v>47.93649152855567</v>
+        <v>47.51720013640395</v>
       </c>
       <c r="E28">
-        <v>2.214</v>
+        <v>2.803000000000001</v>
       </c>
       <c r="F28">
-        <v>15.314</v>
+        <v>15.903</v>
       </c>
       <c r="G28">
         <v>0.573</v>
@@ -3565,37 +3565,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M28">
-        <v>2.2480952</v>
+        <v>2.3345604</v>
       </c>
       <c r="N28">
-        <v>-0.2111564244897961</v>
+        <v>-0.2976216244897962</v>
       </c>
       <c r="O28">
-        <v>-0.02111564244897961</v>
+        <v>-0.02976216244897963</v>
       </c>
       <c r="P28">
-        <v>-0.1900407820408165</v>
+        <v>-0.2678594620408166</v>
       </c>
       <c r="Q28">
-        <v>3.619959217959184</v>
+        <v>3.542140537959183</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09528847736200963</v>
+        <v>0.09596640170943441</v>
       </c>
       <c r="T28">
-        <v>0.9919302130350918</v>
+        <v>1.005518298145161</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.09060731838714856</v>
+        <v>0.08725149178021713</v>
       </c>
       <c r="W28">
-        <v>0.1334988456607666</v>
+        <v>0.1339914810066641</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.9060731838714855</v>
+        <v>0.8725149178021712</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1062331731196864</v>
+        <v>0.1072431731196864</v>
       </c>
       <c r="C29">
-        <v>32.18720013640395</v>
+        <v>31.18618006780089</v>
       </c>
       <c r="D29">
-        <v>47.51720013640395</v>
+        <v>47.10518006780089</v>
       </c>
       <c r="E29">
-        <v>2.803000000000001</v>
+        <v>3.392000000000001</v>
       </c>
       <c r="F29">
-        <v>15.903</v>
+        <v>16.492</v>
       </c>
       <c r="G29">
         <v>0.573</v>
@@ -3647,37 +3647,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M29">
-        <v>2.3345604</v>
+        <v>2.421025600000001</v>
       </c>
       <c r="N29">
-        <v>-0.2976216244897962</v>
+        <v>-0.3840868244897964</v>
       </c>
       <c r="O29">
-        <v>-0.02976216244897963</v>
+        <v>-0.03840868244897964</v>
       </c>
       <c r="P29">
-        <v>-0.2678594620408166</v>
+        <v>-0.3456781420408167</v>
       </c>
       <c r="Q29">
-        <v>3.542140537959183</v>
+        <v>3.464321857959183</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09596640170943441</v>
+        <v>0.09666315728873211</v>
       </c>
       <c r="T29">
-        <v>1.005518298145161</v>
+        <v>1.019483830063844</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.08725149178021713</v>
+        <v>0.08413536707378079</v>
       </c>
       <c r="W29">
-        <v>0.1339914810066641</v>
+        <v>0.134448928113569</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.8725149178021712</v>
+        <v>0.8413536707378079</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1072431731196864</v>
+        <v>0.1082531731196864</v>
       </c>
       <c r="C30">
-        <v>31.18618006780089</v>
+        <v>30.19224380052844</v>
       </c>
       <c r="D30">
-        <v>47.10518006780089</v>
+        <v>46.70024380052844</v>
       </c>
       <c r="E30">
-        <v>3.392000000000001</v>
+        <v>3.981000000000003</v>
       </c>
       <c r="F30">
-        <v>16.492</v>
+        <v>17.081</v>
       </c>
       <c r="G30">
         <v>0.573</v>
@@ -3729,37 +3729,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M30">
-        <v>2.421025600000001</v>
+        <v>2.507490800000001</v>
       </c>
       <c r="N30">
-        <v>-0.3840868244897964</v>
+        <v>-0.4705520244897965</v>
       </c>
       <c r="O30">
-        <v>-0.03840868244897964</v>
+        <v>-0.04705520244897965</v>
       </c>
       <c r="P30">
-        <v>-0.3456781420408167</v>
+        <v>-0.4234968220408168</v>
       </c>
       <c r="Q30">
-        <v>3.464321857959183</v>
+        <v>3.386503177959183</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09666315728873211</v>
+        <v>0.0973795397857565</v>
       </c>
       <c r="T30">
-        <v>1.019483830063844</v>
+        <v>1.033842757247842</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.08413536707378079</v>
+        <v>0.08123414751951248</v>
       </c>
       <c r="W30">
-        <v>0.134448928113569</v>
+        <v>0.1348748271441356</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8413536707378079</v>
+        <v>0.8123414751951248</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1082531731196864</v>
+        <v>0.1257007783483153</v>
       </c>
       <c r="C31">
-        <v>30.19224380052845</v>
+        <v>23.56487226649725</v>
       </c>
       <c r="D31">
-        <v>46.70024380052845</v>
+        <v>40.66187226649725</v>
       </c>
       <c r="E31">
-        <v>3.981</v>
+        <v>4.569999999999999</v>
       </c>
       <c r="F31">
-        <v>17.081</v>
+        <v>17.67</v>
       </c>
       <c r="G31">
         <v>0.573</v>
@@ -3811,45 +3811,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M31">
-        <v>2.5074908</v>
+        <v>3.548136</v>
       </c>
       <c r="N31">
-        <v>-0.4705520244897961</v>
+        <v>-1.511197224489796</v>
       </c>
       <c r="O31">
-        <v>-0.04705520244897961</v>
+        <v>-0.1511197224489796</v>
       </c>
       <c r="P31">
-        <v>-0.4234968220408165</v>
+        <v>-1.360077502040816</v>
       </c>
       <c r="Q31">
-        <v>3.386503177959184</v>
+        <v>2.449922497959184</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0973795397857565</v>
+        <v>0.09845582639502291</v>
       </c>
       <c r="T31">
-        <v>1.033842757247842</v>
+        <v>1.055415480082027</v>
       </c>
       <c r="U31">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.0812341475195125</v>
+        <v>0.05740870066734208</v>
       </c>
       <c r="W31">
-        <v>0.1348748271441356</v>
+        <v>0.1892723329059977</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y31">
-        <v>0.812341475195125</v>
+        <v>0.5740870066734207</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1257007783483153</v>
+        <v>0.1272507783483154</v>
       </c>
       <c r="C32">
-        <v>23.56487226649725</v>
+        <v>22.5141043703467</v>
       </c>
       <c r="D32">
-        <v>40.66187226649725</v>
+        <v>40.2001043703467</v>
       </c>
       <c r="E32">
-        <v>4.569999999999999</v>
+        <v>5.159000000000001</v>
       </c>
       <c r="F32">
-        <v>17.67</v>
+        <v>18.259</v>
       </c>
       <c r="G32">
         <v>0.573</v>
@@ -3893,37 +3893,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M32">
-        <v>3.548136</v>
+        <v>3.6664072</v>
       </c>
       <c r="N32">
-        <v>-1.511197224489796</v>
+        <v>-1.629468424489796</v>
       </c>
       <c r="O32">
-        <v>-0.1511197224489796</v>
+        <v>-0.1629468424489796</v>
       </c>
       <c r="P32">
-        <v>-1.360077502040816</v>
+        <v>-1.466521582040816</v>
       </c>
       <c r="Q32">
-        <v>2.449922497959184</v>
+        <v>2.343478417959184</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09845582639502291</v>
+        <v>0.09921895431379138</v>
       </c>
       <c r="T32">
-        <v>1.055415480082027</v>
+        <v>1.070711356604955</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.05740870066734208</v>
+        <v>0.05555680709742781</v>
       </c>
       <c r="W32">
-        <v>0.1892723329059977</v>
+        <v>0.1896441931348365</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5740870066734207</v>
+        <v>0.5555680709742781</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1272507783483154</v>
+        <v>0.1288007783483154</v>
       </c>
       <c r="C33">
-        <v>22.5141043703467</v>
+        <v>21.47370664517676</v>
       </c>
       <c r="D33">
-        <v>40.2001043703467</v>
+        <v>39.74870664517676</v>
       </c>
       <c r="E33">
-        <v>5.159000000000001</v>
+        <v>5.747999999999999</v>
       </c>
       <c r="F33">
-        <v>18.259</v>
+        <v>18.848</v>
       </c>
       <c r="G33">
         <v>0.573</v>
@@ -3975,37 +3975,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M33">
-        <v>3.6664072</v>
+        <v>3.7846784</v>
       </c>
       <c r="N33">
-        <v>-1.629468424489796</v>
+        <v>-1.747739624489796</v>
       </c>
       <c r="O33">
-        <v>-0.1629468424489796</v>
+        <v>-0.1747739624489796</v>
       </c>
       <c r="P33">
-        <v>-1.466521582040816</v>
+        <v>-1.572965662040816</v>
       </c>
       <c r="Q33">
-        <v>2.343478417959184</v>
+        <v>2.237034337959184</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09921895431379138</v>
+        <v>0.1000045271713471</v>
       </c>
       <c r="T33">
-        <v>1.070711356604955</v>
+        <v>1.086457111849145</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.05555680709742781</v>
+        <v>0.05382065687563319</v>
       </c>
       <c r="W33">
-        <v>0.1896441931348365</v>
+        <v>0.1899928120993729</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5555680709742781</v>
+        <v>0.538206568756332</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1288007783483154</v>
+        <v>0.1303507783483153</v>
       </c>
       <c r="C34">
-        <v>21.47370664517676</v>
+        <v>20.44333363721456</v>
       </c>
       <c r="D34">
-        <v>39.74870664517676</v>
+        <v>39.30733363721456</v>
       </c>
       <c r="E34">
-        <v>5.747999999999999</v>
+        <v>6.337000000000002</v>
       </c>
       <c r="F34">
-        <v>18.848</v>
+        <v>19.437</v>
       </c>
       <c r="G34">
         <v>0.573</v>
@@ -4057,37 +4057,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M34">
-        <v>3.7846784</v>
+        <v>3.9029496</v>
       </c>
       <c r="N34">
-        <v>-1.747739624489796</v>
+        <v>-1.866010824489796</v>
       </c>
       <c r="O34">
-        <v>-0.1747739624489796</v>
+        <v>-0.1866010824489796</v>
       </c>
       <c r="P34">
-        <v>-1.572965662040816</v>
+        <v>-1.679409742040817</v>
       </c>
       <c r="Q34">
-        <v>2.237034337959184</v>
+        <v>2.130590257959184</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1000045271713471</v>
+        <v>0.1008135499649493</v>
       </c>
       <c r="T34">
-        <v>1.086457111849145</v>
+        <v>1.102672889637938</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.05382065687563319</v>
+        <v>0.05218972787940188</v>
       </c>
       <c r="W34">
-        <v>0.1899928120993729</v>
+        <v>0.1903203026418161</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.538206568756332</v>
+        <v>0.5218972787940188</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1303507783483153</v>
+        <v>0.1319007783483154</v>
       </c>
       <c r="C35">
-        <v>20.44333363721456</v>
+        <v>19.42265506797149</v>
       </c>
       <c r="D35">
-        <v>39.30733363721456</v>
+        <v>38.87565506797149</v>
       </c>
       <c r="E35">
-        <v>6.337000000000002</v>
+        <v>6.926</v>
       </c>
       <c r="F35">
-        <v>19.437</v>
+        <v>20.026</v>
       </c>
       <c r="G35">
         <v>0.573</v>
@@ -4139,37 +4139,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M35">
-        <v>3.9029496</v>
+        <v>4.0212208</v>
       </c>
       <c r="N35">
-        <v>-1.866010824489796</v>
+        <v>-1.984282024489796</v>
       </c>
       <c r="O35">
-        <v>-0.1866010824489796</v>
+        <v>-0.1984282024489796</v>
       </c>
       <c r="P35">
-        <v>-1.679409742040817</v>
+        <v>-1.785853822040816</v>
       </c>
       <c r="Q35">
-        <v>2.130590257959184</v>
+        <v>2.024146177959184</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1008135499649493</v>
+        <v>0.1016470886007819</v>
       </c>
       <c r="T35">
-        <v>1.102672889637938</v>
+        <v>1.119380054632453</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.05218972787940188</v>
+        <v>0.05065473588294889</v>
       </c>
       <c r="W35">
-        <v>0.1903203026418161</v>
+        <v>0.1906285290347039</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5218972787940188</v>
+        <v>0.5065473588294889</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1319007783483154</v>
+        <v>0.14579665492802</v>
       </c>
       <c r="C36">
-        <v>19.42265506797149</v>
+        <v>15.34918850870262</v>
       </c>
       <c r="D36">
-        <v>38.87565506797149</v>
+        <v>35.39118850870262</v>
       </c>
       <c r="E36">
-        <v>6.926</v>
+        <v>7.515000000000002</v>
       </c>
       <c r="F36">
-        <v>20.026</v>
+        <v>20.615</v>
       </c>
       <c r="G36">
         <v>0.573</v>
@@ -4221,45 +4221,45 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M36">
-        <v>4.0212208</v>
+        <v>4.861017</v>
       </c>
       <c r="N36">
-        <v>-1.984282024489796</v>
+        <v>-2.824078224489796</v>
       </c>
       <c r="O36">
-        <v>-0.1984282024489796</v>
+        <v>-0.2824078224489796</v>
       </c>
       <c r="P36">
-        <v>-1.785853822040816</v>
+        <v>-2.541670402040817</v>
       </c>
       <c r="Q36">
-        <v>2.024146177959184</v>
+        <v>1.268329597959184</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1016470886007819</v>
+        <v>0.1026537770095703</v>
       </c>
       <c r="T36">
-        <v>1.119380054632453</v>
+        <v>1.139557774801229</v>
       </c>
       <c r="U36">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.05065473588294889</v>
+        <v>0.04190355177754376</v>
       </c>
       <c r="W36">
-        <v>0.1906285290347039</v>
+        <v>0.2259191424908552</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.5065473588294889</v>
+        <v>0.4190355177754376</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.14579665492802</v>
+        <v>0.14769665492802</v>
       </c>
       <c r="C37">
-        <v>15.34918850870262</v>
+        <v>14.33170777994823</v>
       </c>
       <c r="D37">
-        <v>35.39118850870262</v>
+        <v>34.96270777994823</v>
       </c>
       <c r="E37">
-        <v>7.515000000000002</v>
+        <v>8.104000000000001</v>
       </c>
       <c r="F37">
-        <v>20.615</v>
+        <v>21.204</v>
       </c>
       <c r="G37">
         <v>0.573</v>
@@ -4303,37 +4303,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M37">
-        <v>4.861017</v>
+        <v>4.9999032</v>
       </c>
       <c r="N37">
-        <v>-2.824078224489796</v>
+        <v>-2.962964424489796</v>
       </c>
       <c r="O37">
-        <v>-0.2824078224489796</v>
+        <v>-0.2962964424489796</v>
       </c>
       <c r="P37">
-        <v>-2.541670402040817</v>
+        <v>-2.666667982040817</v>
       </c>
       <c r="Q37">
-        <v>1.268329597959184</v>
+        <v>1.143332017959183</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1026537770095703</v>
+        <v>0.1035421172753448</v>
       </c>
       <c r="T37">
-        <v>1.139557774801229</v>
+        <v>1.157363365032498</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04190355177754376</v>
+        <v>0.04073956422816755</v>
       </c>
       <c r="W37">
-        <v>0.2259191424908552</v>
+        <v>0.2261936107549981</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4190355177754376</v>
+        <v>0.4073956422816754</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.14769665492802</v>
+        <v>0.14959665492802</v>
       </c>
       <c r="C38">
-        <v>14.33170777994824</v>
+        <v>13.32447816399429</v>
       </c>
       <c r="D38">
-        <v>34.96270777994823</v>
+        <v>34.54447816399428</v>
       </c>
       <c r="E38">
-        <v>8.103999999999997</v>
+        <v>8.693</v>
       </c>
       <c r="F38">
-        <v>21.204</v>
+        <v>21.793</v>
       </c>
       <c r="G38">
         <v>0.573</v>
@@ -4385,37 +4385,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M38">
-        <v>4.999903199999999</v>
+        <v>5.1387894</v>
       </c>
       <c r="N38">
-        <v>-2.962964424489795</v>
+        <v>-3.101850624489796</v>
       </c>
       <c r="O38">
-        <v>-0.2962964424489795</v>
+        <v>-0.3101850624489796</v>
       </c>
       <c r="P38">
-        <v>-2.666667982040816</v>
+        <v>-2.791665562040817</v>
       </c>
       <c r="Q38">
-        <v>1.143332017959184</v>
+        <v>1.018334437959183</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1035421172753448</v>
+        <v>0.1044586588193979</v>
       </c>
       <c r="T38">
-        <v>1.157363365032498</v>
+        <v>1.175734212096506</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04073956422816755</v>
+        <v>0.03963849492470355</v>
       </c>
       <c r="W38">
-        <v>0.2261936107549981</v>
+        <v>0.2264532428967549</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4073956422816755</v>
+        <v>0.3963849492470355</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.14959665492802</v>
+        <v>0.15149665492802</v>
       </c>
       <c r="C39">
-        <v>13.32447816399429</v>
+        <v>12.32713613296799</v>
       </c>
       <c r="D39">
-        <v>34.54447816399428</v>
+        <v>34.13613613296799</v>
       </c>
       <c r="E39">
-        <v>8.693</v>
+        <v>9.282000000000002</v>
       </c>
       <c r="F39">
-        <v>21.793</v>
+        <v>22.382</v>
       </c>
       <c r="G39">
         <v>0.573</v>
@@ -4467,37 +4467,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M39">
-        <v>5.1387894</v>
+        <v>5.2776756</v>
       </c>
       <c r="N39">
-        <v>-3.101850624489796</v>
+        <v>-3.240736824489796</v>
       </c>
       <c r="O39">
-        <v>-0.3101850624489796</v>
+        <v>-0.3240736824489796</v>
       </c>
       <c r="P39">
-        <v>-2.791665562040817</v>
+        <v>-2.916663142040816</v>
       </c>
       <c r="Q39">
-        <v>1.018334437959183</v>
+        <v>0.8933368579591838</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1044586588193979</v>
+        <v>0.1054047662197108</v>
       </c>
       <c r="T39">
-        <v>1.175734212096506</v>
+        <v>1.194697667130321</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03963849492470355</v>
+        <v>0.03859537663721135</v>
       </c>
       <c r="W39">
-        <v>0.2264532428967549</v>
+        <v>0.2266992101889456</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3963849492470355</v>
+        <v>0.3859537663721135</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.15149665492802</v>
+        <v>0.15339665492802</v>
       </c>
       <c r="C40">
-        <v>12.32713613296799</v>
+        <v>11.33933514689157</v>
       </c>
       <c r="D40">
-        <v>34.13613613296799</v>
+        <v>33.73733514689157</v>
       </c>
       <c r="E40">
-        <v>9.282000000000002</v>
+        <v>9.871</v>
       </c>
       <c r="F40">
-        <v>22.382</v>
+        <v>22.971</v>
       </c>
       <c r="G40">
         <v>0.573</v>
@@ -4549,37 +4549,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M40">
-        <v>5.2776756</v>
+        <v>5.4165618</v>
       </c>
       <c r="N40">
-        <v>-3.240736824489796</v>
+        <v>-3.379623024489796</v>
       </c>
       <c r="O40">
-        <v>-0.3240736824489796</v>
+        <v>-0.3379623024489796</v>
       </c>
       <c r="P40">
-        <v>-2.916663142040816</v>
+        <v>-3.041660722040816</v>
       </c>
       <c r="Q40">
-        <v>0.8933368579591838</v>
+        <v>0.7683392779591838</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1054047662197108</v>
+        <v>0.106381893534788</v>
       </c>
       <c r="T40">
-        <v>1.194697667130321</v>
+        <v>1.214282874788195</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03859537663721135</v>
+        <v>0.03760575159523158</v>
       </c>
       <c r="W40">
-        <v>0.2266992101889456</v>
+        <v>0.2269325637738444</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3859537663721135</v>
+        <v>0.3760575159523157</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.15339665492802</v>
+        <v>0.15529665492802</v>
       </c>
       <c r="C41">
-        <v>11.33933514689157</v>
+        <v>10.360744672822</v>
       </c>
       <c r="D41">
-        <v>33.73733514689157</v>
+        <v>33.347744672822</v>
       </c>
       <c r="E41">
-        <v>9.871</v>
+        <v>10.46</v>
       </c>
       <c r="F41">
-        <v>22.971</v>
+        <v>23.56</v>
       </c>
       <c r="G41">
         <v>0.573</v>
@@ -4631,37 +4631,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M41">
-        <v>5.4165618</v>
+        <v>5.555448000000001</v>
       </c>
       <c r="N41">
-        <v>-3.379623024489796</v>
+        <v>-3.518509224489797</v>
       </c>
       <c r="O41">
-        <v>-0.3379623024489796</v>
+        <v>-0.3518509224489797</v>
       </c>
       <c r="P41">
-        <v>-3.041660722040816</v>
+        <v>-3.166658302040817</v>
       </c>
       <c r="Q41">
-        <v>0.7683392779591838</v>
+        <v>0.6433416979591828</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.106381893534788</v>
+        <v>0.1073915917603678</v>
       </c>
       <c r="T41">
-        <v>1.214282874788195</v>
+        <v>1.234520922701332</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03760575159523158</v>
+        <v>0.03666560780535078</v>
       </c>
       <c r="W41">
-        <v>0.2269325637738444</v>
+        <v>0.2271542496794983</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3760575159523157</v>
+        <v>0.3666560780535078</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.15529665492802</v>
+        <v>0.15719665492802</v>
       </c>
       <c r="C42">
-        <v>10.360744672822</v>
+        <v>9.391049271175397</v>
       </c>
       <c r="D42">
-        <v>33.347744672822</v>
+        <v>32.9670492711754</v>
       </c>
       <c r="E42">
-        <v>10.46</v>
+        <v>11.049</v>
       </c>
       <c r="F42">
-        <v>23.56</v>
+        <v>24.149</v>
       </c>
       <c r="G42">
         <v>0.573</v>
@@ -4713,37 +4713,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M42">
-        <v>5.555448000000001</v>
+        <v>5.6943342</v>
       </c>
       <c r="N42">
-        <v>-3.518509224489797</v>
+        <v>-3.657395424489796</v>
       </c>
       <c r="O42">
-        <v>-0.3518509224489797</v>
+        <v>-0.3657395424489796</v>
       </c>
       <c r="P42">
-        <v>-3.166658302040817</v>
+        <v>-3.291655882040816</v>
       </c>
       <c r="Q42">
-        <v>0.6433416979591828</v>
+        <v>0.5183441179591837</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1073915917603678</v>
+        <v>0.1084355170444419</v>
       </c>
       <c r="T42">
-        <v>1.234520922701332</v>
+        <v>1.255445006136947</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03666560780535078</v>
+        <v>0.03577132468814711</v>
       </c>
       <c r="W42">
-        <v>0.2271542496794983</v>
+        <v>0.2273651216385349</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3666560780535078</v>
+        <v>0.3577132468814711</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.15719665492802</v>
+        <v>0.1590966549280201</v>
       </c>
       <c r="C43">
-        <v>9.391049271175397</v>
+        <v>8.429947743927659</v>
       </c>
       <c r="D43">
-        <v>32.9670492711754</v>
+        <v>32.59494774392766</v>
       </c>
       <c r="E43">
-        <v>11.049</v>
+        <v>11.638</v>
       </c>
       <c r="F43">
-        <v>24.149</v>
+        <v>24.738</v>
       </c>
       <c r="G43">
         <v>0.573</v>
@@ -4795,37 +4795,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M43">
-        <v>5.6943342</v>
+        <v>5.833220400000001</v>
       </c>
       <c r="N43">
-        <v>-3.657395424489796</v>
+        <v>-3.796281624489797</v>
       </c>
       <c r="O43">
-        <v>-0.3657395424489796</v>
+        <v>-0.3796281624489797</v>
       </c>
       <c r="P43">
-        <v>-3.291655882040816</v>
+        <v>-3.416653462040817</v>
       </c>
       <c r="Q43">
-        <v>0.5183441179591837</v>
+        <v>0.3933465379591827</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1084355170444419</v>
+        <v>0.1095154397521047</v>
       </c>
       <c r="T43">
-        <v>1.255445006136947</v>
+        <v>1.277090609691033</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03577132468814711</v>
+        <v>0.03491962648128646</v>
       </c>
       <c r="W43">
-        <v>0.2273651216385349</v>
+        <v>0.2275659520757127</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3577132468814711</v>
+        <v>0.3491962648128646</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.15909665492802</v>
+        <v>0.16099665492802</v>
       </c>
       <c r="C44">
-        <v>8.429947743927663</v>
+        <v>7.477152339857291</v>
       </c>
       <c r="D44">
-        <v>32.59494774392766</v>
+        <v>32.23115233985729</v>
       </c>
       <c r="E44">
-        <v>11.638</v>
+        <v>12.227</v>
       </c>
       <c r="F44">
-        <v>24.738</v>
+        <v>25.327</v>
       </c>
       <c r="G44">
         <v>0.573</v>
@@ -4877,37 +4877,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M44">
-        <v>5.8332204</v>
+        <v>5.9721066</v>
       </c>
       <c r="N44">
-        <v>-3.796281624489796</v>
+        <v>-3.935167824489796</v>
       </c>
       <c r="O44">
-        <v>-0.3796281624489796</v>
+        <v>-0.3935167824489796</v>
       </c>
       <c r="P44">
-        <v>-3.416653462040816</v>
+        <v>-3.541651042040816</v>
       </c>
       <c r="Q44">
-        <v>0.3933465379591836</v>
+        <v>0.268348957959184</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1095154397521046</v>
+        <v>0.1106332544845977</v>
       </c>
       <c r="T44">
-        <v>1.277090609691033</v>
+        <v>1.299495708106665</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03491962648128646</v>
+        <v>0.03410754214451236</v>
       </c>
       <c r="W44">
-        <v>0.2275659520757127</v>
+        <v>0.227757441562324</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3491962648128646</v>
+        <v>0.3410754214451236</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.16099665492802</v>
+        <v>0.16289665492802</v>
       </c>
       <c r="C45">
-        <v>7.477152339857291</v>
+        <v>6.532388012422839</v>
       </c>
       <c r="D45">
-        <v>32.23115233985729</v>
+        <v>31.87538801242284</v>
       </c>
       <c r="E45">
-        <v>12.227</v>
+        <v>12.816</v>
       </c>
       <c r="F45">
-        <v>25.327</v>
+        <v>25.916</v>
       </c>
       <c r="G45">
         <v>0.573</v>
@@ -4959,37 +4959,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M45">
-        <v>5.9721066</v>
+        <v>6.1109928</v>
       </c>
       <c r="N45">
-        <v>-3.935167824489796</v>
+        <v>-4.074054024489795</v>
       </c>
       <c r="O45">
-        <v>-0.3935167824489796</v>
+        <v>-0.4074054024489795</v>
       </c>
       <c r="P45">
-        <v>-3.541651042040816</v>
+        <v>-3.666648622040816</v>
       </c>
       <c r="Q45">
-        <v>0.268348957959184</v>
+        <v>0.1433513779591844</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1106332544845977</v>
+        <v>0.1117909911718227</v>
       </c>
       <c r="T45">
-        <v>1.299495708106665</v>
+        <v>1.32270098860857</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03410754214451236</v>
+        <v>0.03333237073213708</v>
       </c>
       <c r="W45">
-        <v>0.227757441562324</v>
+        <v>0.2279402269813621</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3410754214451236</v>
+        <v>0.3333237073213708</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.16289665492802</v>
+        <v>0.16479665492802</v>
       </c>
       <c r="C46">
-        <v>6.532388012422839</v>
+        <v>5.595391726252753</v>
       </c>
       <c r="D46">
-        <v>31.87538801242284</v>
+        <v>31.52739172625275</v>
       </c>
       <c r="E46">
-        <v>12.816</v>
+        <v>13.405</v>
       </c>
       <c r="F46">
-        <v>25.916</v>
+        <v>26.505</v>
       </c>
       <c r="G46">
         <v>0.573</v>
@@ -5041,37 +5041,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M46">
-        <v>6.1109928</v>
+        <v>6.249879</v>
       </c>
       <c r="N46">
-        <v>-4.074054024489795</v>
+        <v>-4.212940224489795</v>
       </c>
       <c r="O46">
-        <v>-0.4074054024489795</v>
+        <v>-0.4212940224489796</v>
       </c>
       <c r="P46">
-        <v>-3.666648622040816</v>
+        <v>-3.791646202040816</v>
       </c>
       <c r="Q46">
-        <v>0.1433513779591844</v>
+        <v>0.01835379795918435</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1117909911718227</v>
+        <v>0.1129908273749467</v>
       </c>
       <c r="T46">
-        <v>1.32270098860857</v>
+        <v>1.346750097492361</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03333237073213708</v>
+        <v>0.03259165138253403</v>
       </c>
       <c r="W46">
-        <v>0.2279402269813621</v>
+        <v>0.2281148886039985</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3333237073213708</v>
+        <v>0.3259165138253404</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.16479665492802</v>
+        <v>0.16669665492802</v>
       </c>
       <c r="C47">
-        <v>5.595391726252753</v>
+        <v>4.665911808572453</v>
       </c>
       <c r="D47">
-        <v>31.52739172625275</v>
+        <v>31.18691180857245</v>
       </c>
       <c r="E47">
-        <v>13.405</v>
+        <v>13.994</v>
       </c>
       <c r="F47">
-        <v>26.505</v>
+        <v>27.094</v>
       </c>
       <c r="G47">
         <v>0.573</v>
@@ -5123,37 +5123,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M47">
-        <v>6.249879</v>
+        <v>6.388765200000001</v>
       </c>
       <c r="N47">
-        <v>-4.212940224489795</v>
+        <v>-4.351826424489797</v>
       </c>
       <c r="O47">
-        <v>-0.4212940224489796</v>
+        <v>-0.4351826424489798</v>
       </c>
       <c r="P47">
-        <v>-3.791646202040816</v>
+        <v>-3.916643782040818</v>
       </c>
       <c r="Q47">
-        <v>0.01835379795918435</v>
+        <v>-0.1066437820408175</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1129908273749467</v>
+        <v>0.1142351019559643</v>
       </c>
       <c r="T47">
-        <v>1.346750097492361</v>
+        <v>1.371689914112591</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03259165138253403</v>
+        <v>0.03188313722204416</v>
       </c>
       <c r="W47">
-        <v>0.2281148886039985</v>
+        <v>0.228281956243042</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3259165138253404</v>
+        <v>0.3188313722204416</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.16669665492802</v>
+        <v>0.16859665492802</v>
       </c>
       <c r="C48">
-        <v>4.665911808572453</v>
+        <v>3.743707342208065</v>
       </c>
       <c r="D48">
-        <v>31.18691180857245</v>
+        <v>30.85370734220806</v>
       </c>
       <c r="E48">
-        <v>13.994</v>
+        <v>14.583</v>
       </c>
       <c r="F48">
-        <v>27.094</v>
+        <v>27.683</v>
       </c>
       <c r="G48">
         <v>0.573</v>
@@ -5205,37 +5205,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M48">
-        <v>6.388765200000001</v>
+        <v>6.5276514</v>
       </c>
       <c r="N48">
-        <v>-4.351826424489797</v>
+        <v>-4.490712624489795</v>
       </c>
       <c r="O48">
-        <v>-0.4351826424489798</v>
+        <v>-0.4490712624489795</v>
       </c>
       <c r="P48">
-        <v>-3.916643782040818</v>
+        <v>-4.041641362040815</v>
       </c>
       <c r="Q48">
-        <v>-0.1066437820408175</v>
+        <v>-0.2316413620408153</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1142351019559643</v>
+        <v>0.1155263302947561</v>
       </c>
       <c r="T48">
-        <v>1.371689914112591</v>
+        <v>1.3975708558883</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03188313722204416</v>
+        <v>0.03120477260029854</v>
       </c>
       <c r="W48">
-        <v>0.228281956243042</v>
+        <v>0.2284419146208496</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3188313722204416</v>
+        <v>0.3120477260029855</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.16859665492802</v>
+        <v>0.17049665492802</v>
       </c>
       <c r="C49">
-        <v>3.743707342208065</v>
+        <v>2.828547597090061</v>
       </c>
       <c r="D49">
-        <v>30.85370734220806</v>
+        <v>30.52754759709006</v>
       </c>
       <c r="E49">
-        <v>14.583</v>
+        <v>15.172</v>
       </c>
       <c r="F49">
-        <v>27.683</v>
+        <v>28.272</v>
       </c>
       <c r="G49">
         <v>0.573</v>
@@ -5287,37 +5287,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M49">
-        <v>6.5276514</v>
+        <v>6.666537600000001</v>
       </c>
       <c r="N49">
-        <v>-4.490712624489795</v>
+        <v>-4.629598824489797</v>
       </c>
       <c r="O49">
-        <v>-0.4490712624489795</v>
+        <v>-0.4629598824489797</v>
       </c>
       <c r="P49">
-        <v>-4.041641362040815</v>
+        <v>-4.166638942040818</v>
       </c>
       <c r="Q49">
-        <v>-0.2316413620408153</v>
+        <v>-0.3566389420408176</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1155263302947561</v>
+        <v>0.1168672212619629</v>
       </c>
       <c r="T49">
-        <v>1.3975708558883</v>
+        <v>1.424447218501536</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03120477260029854</v>
+        <v>0.03055467317112565</v>
       </c>
       <c r="W49">
-        <v>0.2284419146208496</v>
+        <v>0.2285952080662486</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3120477260029855</v>
+        <v>0.3055467317112565</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.17049665492802</v>
+        <v>0.17239665492802</v>
       </c>
       <c r="C50">
-        <v>2.828547597090065</v>
+        <v>1.920211497437727</v>
       </c>
       <c r="D50">
-        <v>30.52754759709006</v>
+        <v>30.20821149743772</v>
       </c>
       <c r="E50">
-        <v>15.172</v>
+        <v>15.761</v>
       </c>
       <c r="F50">
-        <v>28.272</v>
+        <v>28.861</v>
       </c>
       <c r="G50">
         <v>0.573</v>
@@ -5369,37 +5369,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M50">
-        <v>6.6665376</v>
+        <v>6.8054238</v>
       </c>
       <c r="N50">
-        <v>-4.629598824489795</v>
+        <v>-4.768485024489795</v>
       </c>
       <c r="O50">
-        <v>-0.4629598824489796</v>
+        <v>-0.4768485024489795</v>
       </c>
       <c r="P50">
-        <v>-4.166638942040816</v>
+        <v>-4.291636522040815</v>
       </c>
       <c r="Q50">
-        <v>-0.3566389420408158</v>
+        <v>-0.4816365220408154</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1168672212619629</v>
+        <v>0.1182606961886681</v>
       </c>
       <c r="T50">
-        <v>1.424447218501536</v>
+        <v>1.452377556119214</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03055467317112566</v>
+        <v>0.02993110841253126</v>
       </c>
       <c r="W50">
-        <v>0.2285952080662486</v>
+        <v>0.2287422446363251</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3055467317112567</v>
+        <v>0.2993110841253126</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.17239665492802</v>
+        <v>0.17429665492802</v>
       </c>
       <c r="C51">
-        <v>1.920211497437727</v>
+        <v>1.018487122038881</v>
       </c>
       <c r="D51">
-        <v>30.20821149743772</v>
+        <v>29.89548712203888</v>
       </c>
       <c r="E51">
-        <v>15.761</v>
+        <v>16.35</v>
       </c>
       <c r="F51">
-        <v>28.861</v>
+        <v>29.45</v>
       </c>
       <c r="G51">
         <v>0.573</v>
@@ -5451,37 +5451,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M51">
-        <v>6.8054238</v>
+        <v>6.94431</v>
       </c>
       <c r="N51">
-        <v>-4.768485024489795</v>
+        <v>-4.907371224489795</v>
       </c>
       <c r="O51">
-        <v>-0.4768485024489795</v>
+        <v>-0.4907371224489795</v>
       </c>
       <c r="P51">
-        <v>-4.291636522040815</v>
+        <v>-4.416634102040816</v>
       </c>
       <c r="Q51">
-        <v>-0.4816365220408154</v>
+        <v>-0.6066341020408159</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1182606961886681</v>
+        <v>0.1197099101124414</v>
       </c>
       <c r="T51">
-        <v>1.452377556119214</v>
+        <v>1.481425107241598</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02993110841253126</v>
+        <v>0.02933248624428063</v>
       </c>
       <c r="W51">
-        <v>0.2287422446363251</v>
+        <v>0.2288833997435986</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2993110841253126</v>
+        <v>0.2933248624428064</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.17429665492802</v>
+        <v>0.17619665492802</v>
       </c>
       <c r="C52">
-        <v>1.018487122038881</v>
+        <v>0.1231712352510179</v>
       </c>
       <c r="D52">
-        <v>29.89548712203888</v>
+        <v>29.58917123525102</v>
       </c>
       <c r="E52">
-        <v>16.35</v>
+        <v>16.939</v>
       </c>
       <c r="F52">
-        <v>29.45</v>
+        <v>30.039</v>
       </c>
       <c r="G52">
         <v>0.573</v>
@@ -5533,37 +5533,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M52">
-        <v>6.94431</v>
+        <v>7.083196200000001</v>
       </c>
       <c r="N52">
-        <v>-4.907371224489795</v>
+        <v>-5.046257424489797</v>
       </c>
       <c r="O52">
-        <v>-0.4907371224489795</v>
+        <v>-0.5046257424489797</v>
       </c>
       <c r="P52">
-        <v>-4.416634102040816</v>
+        <v>-4.541631682040817</v>
       </c>
       <c r="Q52">
-        <v>-0.6066341020408159</v>
+        <v>-0.7316316820408173</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1197099101124414</v>
+        <v>0.1212182756249402</v>
       </c>
       <c r="T52">
-        <v>1.481425107241598</v>
+        <v>1.511658272695508</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02933248624428063</v>
+        <v>0.02875733945517708</v>
       </c>
       <c r="W52">
-        <v>0.2288833997435986</v>
+        <v>0.2290190193564692</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2933248624428064</v>
+        <v>0.2875733945517708</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.17619665492802</v>
+        <v>0.17809665492802</v>
       </c>
       <c r="C53">
-        <v>0.1231712352510179</v>
+        <v>-0.7659311534572062</v>
       </c>
       <c r="D53">
-        <v>29.58917123525102</v>
+        <v>29.28906884654279</v>
       </c>
       <c r="E53">
-        <v>16.939</v>
+        <v>17.528</v>
       </c>
       <c r="F53">
-        <v>30.039</v>
+        <v>30.628</v>
       </c>
       <c r="G53">
         <v>0.573</v>
@@ -5615,37 +5615,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M53">
-        <v>7.083196200000001</v>
+        <v>7.222082400000001</v>
       </c>
       <c r="N53">
-        <v>-5.046257424489797</v>
+        <v>-5.185143624489797</v>
       </c>
       <c r="O53">
-        <v>-0.5046257424489797</v>
+        <v>-0.5185143624489797</v>
       </c>
       <c r="P53">
-        <v>-4.541631682040817</v>
+        <v>-4.666629262040817</v>
       </c>
       <c r="Q53">
-        <v>-0.7316316820408173</v>
+        <v>-0.8566292620408169</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1212182756249402</v>
+        <v>0.1227894897004598</v>
       </c>
       <c r="T53">
-        <v>1.511658272695508</v>
+        <v>1.543151153376664</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02875733945517708</v>
+        <v>0.02820431369642368</v>
       </c>
       <c r="W53">
-        <v>0.2290190193564692</v>
+        <v>0.2291494228303833</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2875733945517708</v>
+        <v>0.2820431369642368</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.17809665492802</v>
+        <v>0.17999665492802</v>
       </c>
       <c r="C54">
-        <v>-0.7659311534572062</v>
+        <v>-1.64900720342991</v>
       </c>
       <c r="D54">
-        <v>29.28906884654279</v>
+        <v>28.99499279657009</v>
       </c>
       <c r="E54">
-        <v>17.528</v>
+        <v>18.117</v>
       </c>
       <c r="F54">
-        <v>30.628</v>
+        <v>31.217</v>
       </c>
       <c r="G54">
         <v>0.573</v>
@@ -5697,37 +5697,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M54">
-        <v>7.222082400000001</v>
+        <v>7.360968600000001</v>
       </c>
       <c r="N54">
-        <v>-5.185143624489797</v>
+        <v>-5.324029824489797</v>
       </c>
       <c r="O54">
-        <v>-0.5185143624489797</v>
+        <v>-0.5324029824489797</v>
       </c>
       <c r="P54">
-        <v>-4.666629262040817</v>
+        <v>-4.791626842040817</v>
       </c>
       <c r="Q54">
-        <v>-0.8566292620408169</v>
+        <v>-0.9816268420408174</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1227894897004598</v>
+        <v>0.1244275639494058</v>
       </c>
       <c r="T54">
-        <v>1.543151153376664</v>
+        <v>1.575984156639998</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02820431369642368</v>
+        <v>0.02767215683422701</v>
       </c>
       <c r="W54">
-        <v>0.2291494228303833</v>
+        <v>0.2292749054184893</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2820431369642368</v>
+        <v>0.27672156834227</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.17999665492802</v>
+        <v>0.18189665492802</v>
       </c>
       <c r="C55">
-        <v>-1.64900720342991</v>
+        <v>-2.526236632059941</v>
       </c>
       <c r="D55">
-        <v>28.99499279657009</v>
+        <v>28.70676336794006</v>
       </c>
       <c r="E55">
-        <v>18.117</v>
+        <v>18.706</v>
       </c>
       <c r="F55">
-        <v>31.217</v>
+        <v>31.806</v>
       </c>
       <c r="G55">
         <v>0.573</v>
@@ -5779,37 +5779,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M55">
-        <v>7.360968600000001</v>
+        <v>7.4998548</v>
       </c>
       <c r="N55">
-        <v>-5.324029824489797</v>
+        <v>-5.462916024489797</v>
       </c>
       <c r="O55">
-        <v>-0.5324029824489797</v>
+        <v>-0.5462916024489797</v>
       </c>
       <c r="P55">
-        <v>-4.791626842040817</v>
+        <v>-4.916624422040817</v>
       </c>
       <c r="Q55">
-        <v>-0.9816268420408174</v>
+        <v>-1.106624422040817</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1244275639494058</v>
+        <v>0.1261368588178711</v>
       </c>
       <c r="T55">
-        <v>1.575984156639998</v>
+        <v>1.610244681784345</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02767215683422701</v>
+        <v>0.02715970948544503</v>
       </c>
       <c r="W55">
-        <v>0.2292749054184893</v>
+        <v>0.2293957405033321</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.27672156834227</v>
+        <v>0.2715970948544502</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.18189665492802</v>
+        <v>0.18379665492802</v>
       </c>
       <c r="C56">
-        <v>-2.526236632059941</v>
+        <v>-3.397792081037775</v>
       </c>
       <c r="D56">
-        <v>28.70676336794006</v>
+        <v>28.42420791896223</v>
       </c>
       <c r="E56">
-        <v>18.706</v>
+        <v>19.295</v>
       </c>
       <c r="F56">
-        <v>31.806</v>
+        <v>32.395</v>
       </c>
       <c r="G56">
         <v>0.573</v>
@@ -5861,37 +5861,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M56">
-        <v>7.4998548</v>
+        <v>7.638741000000001</v>
       </c>
       <c r="N56">
-        <v>-5.462916024489797</v>
+        <v>-5.601802224489797</v>
       </c>
       <c r="O56">
-        <v>-0.5462916024489797</v>
+        <v>-0.5601802224489797</v>
       </c>
       <c r="P56">
-        <v>-4.916624422040817</v>
+        <v>-5.041622002040817</v>
       </c>
       <c r="Q56">
-        <v>-1.106624422040817</v>
+        <v>-1.231622002040817</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1261368588178711</v>
+        <v>0.1279221223471571</v>
       </c>
       <c r="T56">
-        <v>1.610244681784345</v>
+        <v>1.646027896935109</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02715970948544503</v>
+        <v>0.02666589658570966</v>
       </c>
       <c r="W56">
-        <v>0.2293957405033321</v>
+        <v>0.2295121815850897</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2715970948544502</v>
+        <v>0.2666589658570967</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.18379665492802</v>
+        <v>0.18569665492802</v>
       </c>
       <c r="C57">
-        <v>-3.397792081037775</v>
+        <v>-4.263839461181608</v>
       </c>
       <c r="D57">
-        <v>28.42420791896223</v>
+        <v>28.14716053881839</v>
       </c>
       <c r="E57">
-        <v>19.295</v>
+        <v>19.884</v>
       </c>
       <c r="F57">
-        <v>32.395</v>
+        <v>32.984</v>
       </c>
       <c r="G57">
         <v>0.573</v>
@@ -5943,37 +5943,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M57">
-        <v>7.638741000000001</v>
+        <v>7.7776272</v>
       </c>
       <c r="N57">
-        <v>-5.601802224489797</v>
+        <v>-5.740688424489797</v>
       </c>
       <c r="O57">
-        <v>-0.5601802224489797</v>
+        <v>-0.5740688424489797</v>
       </c>
       <c r="P57">
-        <v>-5.041622002040817</v>
+        <v>-5.166619582040817</v>
       </c>
       <c r="Q57">
-        <v>-1.231622002040817</v>
+        <v>-1.356619582040817</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1279221223471571</v>
+        <v>0.1297885342186834</v>
       </c>
       <c r="T57">
-        <v>1.646027896935109</v>
+        <v>1.683437621865452</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02666589658570966</v>
+        <v>0.02618971986096484</v>
       </c>
       <c r="W57">
-        <v>0.2295121815850897</v>
+        <v>0.2296244640567845</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2666589658570967</v>
+        <v>0.2618971986096484</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.18569665492802</v>
+        <v>0.18759665492802</v>
       </c>
       <c r="C58">
-        <v>-4.263839461181608</v>
+        <v>-5.124538277296121</v>
       </c>
       <c r="D58">
-        <v>28.14716053881839</v>
+        <v>27.87546172270388</v>
       </c>
       <c r="E58">
-        <v>19.884</v>
+        <v>20.473</v>
       </c>
       <c r="F58">
-        <v>32.984</v>
+        <v>33.573</v>
       </c>
       <c r="G58">
         <v>0.573</v>
@@ -6025,37 +6025,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M58">
-        <v>7.7776272</v>
+        <v>7.9165134</v>
       </c>
       <c r="N58">
-        <v>-5.740688424489797</v>
+        <v>-5.879574624489797</v>
       </c>
       <c r="O58">
-        <v>-0.5740688424489797</v>
+        <v>-0.5879574624489797</v>
       </c>
       <c r="P58">
-        <v>-5.166619582040817</v>
+        <v>-5.291617162040817</v>
       </c>
       <c r="Q58">
-        <v>-1.356619582040817</v>
+        <v>-1.481617162040817</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1297885342186834</v>
+        <v>0.1317417559446993</v>
       </c>
       <c r="T58">
-        <v>1.683437621865452</v>
+        <v>1.722587334001858</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02618971986096484</v>
+        <v>0.02573025109147424</v>
       </c>
       <c r="W58">
-        <v>0.2296244640567845</v>
+        <v>0.2297328067926304</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2618971986096484</v>
+        <v>0.2573025109147423</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.18759665492802</v>
+        <v>0.18949665492802</v>
       </c>
       <c r="C59">
-        <v>-5.124538277296121</v>
+        <v>-5.980041934396265</v>
       </c>
       <c r="D59">
-        <v>27.87546172270388</v>
+        <v>27.60895806560374</v>
       </c>
       <c r="E59">
-        <v>20.473</v>
+        <v>21.062</v>
       </c>
       <c r="F59">
-        <v>33.573</v>
+        <v>34.16200000000001</v>
       </c>
       <c r="G59">
         <v>0.573</v>
@@ -6107,37 +6107,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M59">
-        <v>7.9165134</v>
+        <v>8.055399600000001</v>
       </c>
       <c r="N59">
-        <v>-5.879574624489797</v>
+        <v>-6.018460824489797</v>
       </c>
       <c r="O59">
-        <v>-0.5879574624489797</v>
+        <v>-0.6018460824489797</v>
       </c>
       <c r="P59">
-        <v>-5.291617162040817</v>
+        <v>-5.416614742040817</v>
       </c>
       <c r="Q59">
-        <v>-1.481617162040817</v>
+        <v>-1.606614742040817</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1317417559446993</v>
+        <v>0.1337879882290969</v>
       </c>
       <c r="T59">
-        <v>1.722587334001858</v>
+        <v>1.763601318144759</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02573025109147424</v>
+        <v>0.02528662607265571</v>
       </c>
       <c r="W59">
-        <v>0.2297328067926304</v>
+        <v>0.2298374135720678</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2573025109147423</v>
+        <v>0.2528662607265572</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.18949665492802</v>
+        <v>0.19139665492802</v>
       </c>
       <c r="C60">
-        <v>-5.980041934396258</v>
+        <v>-6.830498026531469</v>
       </c>
       <c r="D60">
-        <v>27.60895806560374</v>
+        <v>27.34750197346853</v>
       </c>
       <c r="E60">
-        <v>21.062</v>
+        <v>21.651</v>
       </c>
       <c r="F60">
-        <v>34.162</v>
+        <v>34.751</v>
       </c>
       <c r="G60">
         <v>0.573</v>
@@ -6189,37 +6189,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M60">
-        <v>8.055399599999999</v>
+        <v>8.194285799999999</v>
       </c>
       <c r="N60">
-        <v>-6.018460824489795</v>
+        <v>-6.157347024489795</v>
       </c>
       <c r="O60">
-        <v>-0.6018460824489795</v>
+        <v>-0.6157347024489795</v>
       </c>
       <c r="P60">
-        <v>-5.416614742040815</v>
+        <v>-5.541612322040815</v>
       </c>
       <c r="Q60">
-        <v>-1.606614742040815</v>
+        <v>-1.731612322040815</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1337879882290969</v>
+        <v>0.1359340367224895</v>
       </c>
       <c r="T60">
-        <v>1.763601318144759</v>
+        <v>1.806615984440973</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02528662607265572</v>
+        <v>0.02485803919006833</v>
       </c>
       <c r="W60">
-        <v>0.2298374135720678</v>
+        <v>0.2299384743589819</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2528662607265573</v>
+        <v>0.2485803919006834</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.19139665492802</v>
+        <v>0.19329665492802</v>
       </c>
       <c r="C61">
-        <v>-6.830498026531469</v>
+        <v>-7.676048609352915</v>
       </c>
       <c r="D61">
-        <v>27.34750197346853</v>
+        <v>27.09095139064708</v>
       </c>
       <c r="E61">
-        <v>21.651</v>
+        <v>22.23999999999999</v>
       </c>
       <c r="F61">
-        <v>34.751</v>
+        <v>35.34</v>
       </c>
       <c r="G61">
         <v>0.573</v>
@@ -6271,37 +6271,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M61">
-        <v>8.194285799999999</v>
+        <v>8.333171999999999</v>
       </c>
       <c r="N61">
-        <v>-6.157347024489795</v>
+        <v>-6.296233224489795</v>
       </c>
       <c r="O61">
-        <v>-0.6157347024489795</v>
+        <v>-0.6296233224489796</v>
       </c>
       <c r="P61">
-        <v>-5.541612322040815</v>
+        <v>-5.666609902040815</v>
       </c>
       <c r="Q61">
-        <v>-1.731612322040815</v>
+        <v>-1.856609902040815</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1359340367224895</v>
+        <v>0.1381873876405517</v>
       </c>
       <c r="T61">
-        <v>1.806615984440973</v>
+        <v>1.851781384051997</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02485803919006833</v>
+        <v>0.02444373853690053</v>
       </c>
       <c r="W61">
-        <v>0.2299384743589819</v>
+        <v>0.2300361664529989</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2485803919006834</v>
+        <v>0.2444373853690053</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.19329665492802</v>
+        <v>0.19519665492802</v>
       </c>
       <c r="C62">
-        <v>-7.676048609352915</v>
+        <v>-8.516830457481369</v>
       </c>
       <c r="D62">
-        <v>27.09095139064708</v>
+        <v>26.83916954251863</v>
       </c>
       <c r="E62">
-        <v>22.23999999999999</v>
+        <v>22.82899999999999</v>
       </c>
       <c r="F62">
-        <v>35.34</v>
+        <v>35.92899999999999</v>
       </c>
       <c r="G62">
         <v>0.573</v>
@@ -6353,37 +6353,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M62">
-        <v>8.333171999999999</v>
+        <v>8.472058199999999</v>
       </c>
       <c r="N62">
-        <v>-6.296233224489795</v>
+        <v>-6.435119424489795</v>
       </c>
       <c r="O62">
-        <v>-0.6296233224489796</v>
+        <v>-0.6435119424489795</v>
       </c>
       <c r="P62">
-        <v>-5.666609902040815</v>
+        <v>-5.791607482040815</v>
       </c>
       <c r="Q62">
-        <v>-1.856609902040815</v>
+        <v>-1.981607482040815</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1381873876405517</v>
+        <v>0.1405562950159505</v>
       </c>
       <c r="T62">
-        <v>1.851781384051997</v>
+        <v>1.899262958002048</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02444373853690053</v>
+        <v>0.02404302151170544</v>
       </c>
       <c r="W62">
-        <v>0.2300361664529989</v>
+        <v>0.2301306555275399</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2444373853690053</v>
+        <v>0.2404302151170544</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.19519665492802</v>
+        <v>0.19709665492802</v>
       </c>
       <c r="C63">
-        <v>-8.516830457481369</v>
+        <v>-9.352975307655512</v>
       </c>
       <c r="D63">
-        <v>26.83916954251863</v>
+        <v>26.59202469234449</v>
       </c>
       <c r="E63">
-        <v>22.82899999999999</v>
+        <v>23.418</v>
       </c>
       <c r="F63">
-        <v>35.92899999999999</v>
+        <v>36.518</v>
       </c>
       <c r="G63">
         <v>0.573</v>
@@ -6435,37 +6435,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M63">
-        <v>8.472058199999999</v>
+        <v>8.610944400000001</v>
       </c>
       <c r="N63">
-        <v>-6.435119424489795</v>
+        <v>-6.574005624489796</v>
       </c>
       <c r="O63">
-        <v>-0.6435119424489795</v>
+        <v>-0.6574005624489797</v>
       </c>
       <c r="P63">
-        <v>-5.791607482040815</v>
+        <v>-5.916605062040817</v>
       </c>
       <c r="Q63">
-        <v>-1.981607482040815</v>
+        <v>-2.106605062040817</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1405562950159505</v>
+        <v>0.1430498817268966</v>
       </c>
       <c r="T63">
-        <v>1.899262958002048</v>
+        <v>1.949243562159997</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02404302151170544</v>
+        <v>0.0236552308421618</v>
       </c>
       <c r="W63">
-        <v>0.2301306555275399</v>
+        <v>0.2302220965674183</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2404302151170544</v>
+        <v>0.236552308421618</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.19709665492802</v>
+        <v>0.19899665492802</v>
       </c>
       <c r="C64">
-        <v>-9.352975307655512</v>
+        <v>-10.18461008856868</v>
       </c>
       <c r="D64">
-        <v>26.59202469234449</v>
+        <v>26.34938991143132</v>
       </c>
       <c r="E64">
-        <v>23.418</v>
+        <v>24.007</v>
       </c>
       <c r="F64">
-        <v>36.518</v>
+        <v>37.107</v>
       </c>
       <c r="G64">
         <v>0.573</v>
@@ -6517,37 +6517,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M64">
-        <v>8.610944400000001</v>
+        <v>8.749830600000001</v>
       </c>
       <c r="N64">
-        <v>-6.574005624489796</v>
+        <v>-6.712891824489796</v>
       </c>
       <c r="O64">
-        <v>-0.6574005624489797</v>
+        <v>-0.6712891824489797</v>
       </c>
       <c r="P64">
-        <v>-5.916605062040817</v>
+        <v>-6.041602642040816</v>
       </c>
       <c r="Q64">
-        <v>-2.106605062040817</v>
+        <v>-2.231602642040816</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1430498817268966</v>
+        <v>0.1456782569087046</v>
       </c>
       <c r="T64">
-        <v>1.949243562159997</v>
+        <v>2.001925820596754</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0236552308421618</v>
+        <v>0.02327975098752431</v>
       </c>
       <c r="W64">
-        <v>0.2302220965674183</v>
+        <v>0.2303106347171418</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.236552308421618</v>
+        <v>0.2327975098752432</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.19899665492802</v>
+        <v>0.20089665492802</v>
       </c>
       <c r="C65">
-        <v>-10.18461008856868</v>
+        <v>-11.01185713823693</v>
       </c>
       <c r="D65">
-        <v>26.34938991143132</v>
+        <v>26.11114286176306</v>
       </c>
       <c r="E65">
-        <v>24.007</v>
+        <v>24.596</v>
       </c>
       <c r="F65">
-        <v>37.107</v>
+        <v>37.696</v>
       </c>
       <c r="G65">
         <v>0.573</v>
@@ -6599,37 +6599,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M65">
-        <v>8.749830600000001</v>
+        <v>8.888716799999999</v>
       </c>
       <c r="N65">
-        <v>-6.712891824489796</v>
+        <v>-6.851778024489795</v>
       </c>
       <c r="O65">
-        <v>-0.6712891824489797</v>
+        <v>-0.6851778024489795</v>
       </c>
       <c r="P65">
-        <v>-6.041602642040816</v>
+        <v>-6.166600222040815</v>
       </c>
       <c r="Q65">
-        <v>-2.231602642040816</v>
+        <v>-2.356600222040815</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1456782569087046</v>
+        <v>0.1484526529339464</v>
       </c>
       <c r="T65">
-        <v>2.001925820596754</v>
+        <v>2.057534871168886</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02327975098752431</v>
+        <v>0.02291600487834424</v>
       </c>
       <c r="W65">
-        <v>0.2303106347171418</v>
+        <v>0.2303964060496864</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2327975098752432</v>
+        <v>0.2291600487834425</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.20089665492802</v>
+        <v>0.20279665492802</v>
       </c>
       <c r="C66">
-        <v>-11.01185713823693</v>
+        <v>-11.83483440968017</v>
       </c>
       <c r="D66">
-        <v>26.11114286176306</v>
+        <v>25.87716559031983</v>
       </c>
       <c r="E66">
-        <v>24.596</v>
+        <v>25.185</v>
       </c>
       <c r="F66">
-        <v>37.696</v>
+        <v>38.285</v>
       </c>
       <c r="G66">
         <v>0.573</v>
@@ -6681,37 +6681,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M66">
-        <v>8.888716799999999</v>
+        <v>9.027603000000001</v>
       </c>
       <c r="N66">
-        <v>-6.851778024489795</v>
+        <v>-6.990664224489796</v>
       </c>
       <c r="O66">
-        <v>-0.6851778024489795</v>
+        <v>-0.6990664224489797</v>
       </c>
       <c r="P66">
-        <v>-6.166600222040815</v>
+        <v>-6.291597802040816</v>
       </c>
       <c r="Q66">
-        <v>-2.356600222040815</v>
+        <v>-2.481597802040816</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1484526529339464</v>
+        <v>0.1513855858749163</v>
       </c>
       <c r="T66">
-        <v>2.057534871168886</v>
+        <v>2.116321581773711</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02291600487834424</v>
+        <v>0.02256345095713895</v>
       </c>
       <c r="W66">
-        <v>0.2303964060496864</v>
+        <v>0.2304795382643066</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2291600487834425</v>
+        <v>0.2256345095713895</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.20279665492802</v>
+        <v>0.20469665492802</v>
       </c>
       <c r="C67">
-        <v>-11.83483440968017</v>
+        <v>-12.6536556656431</v>
       </c>
       <c r="D67">
-        <v>25.87716559031983</v>
+        <v>25.6473443343569</v>
       </c>
       <c r="E67">
-        <v>25.185</v>
+        <v>25.774</v>
       </c>
       <c r="F67">
-        <v>38.285</v>
+        <v>38.874</v>
       </c>
       <c r="G67">
         <v>0.573</v>
@@ -6763,37 +6763,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M67">
-        <v>9.027603000000001</v>
+        <v>9.166489200000001</v>
       </c>
       <c r="N67">
-        <v>-6.990664224489796</v>
+        <v>-7.129550424489796</v>
       </c>
       <c r="O67">
-        <v>-0.6990664224489797</v>
+        <v>-0.7129550424489797</v>
       </c>
       <c r="P67">
-        <v>-6.291597802040816</v>
+        <v>-6.416595382040817</v>
       </c>
       <c r="Q67">
-        <v>-2.481597802040816</v>
+        <v>-2.606595382040817</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1513855858749163</v>
+        <v>0.1544910442830021</v>
       </c>
       <c r="T67">
-        <v>2.116321581773711</v>
+        <v>2.178566334178821</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02256345095713895</v>
+        <v>0.02222158048809138</v>
       </c>
       <c r="W67">
-        <v>0.2304795382643066</v>
+        <v>0.230560151320908</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2256345095713895</v>
+        <v>0.2222158048809139</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.20469665492802</v>
+        <v>0.20659665492802</v>
       </c>
       <c r="C68">
-        <v>-12.6536556656431</v>
+        <v>-13.4684306630314</v>
       </c>
       <c r="D68">
-        <v>25.6473443343569</v>
+        <v>25.4215693369686</v>
       </c>
       <c r="E68">
-        <v>25.774</v>
+        <v>26.363</v>
       </c>
       <c r="F68">
-        <v>38.874</v>
+        <v>39.463</v>
       </c>
       <c r="G68">
         <v>0.573</v>
@@ -6845,37 +6845,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M68">
-        <v>9.166489200000001</v>
+        <v>9.305375400000001</v>
       </c>
       <c r="N68">
-        <v>-7.129550424489796</v>
+        <v>-7.268436624489796</v>
       </c>
       <c r="O68">
-        <v>-0.7129550424489797</v>
+        <v>-0.7268436624489797</v>
       </c>
       <c r="P68">
-        <v>-6.416595382040817</v>
+        <v>-6.541592962040816</v>
       </c>
       <c r="Q68">
-        <v>-2.606595382040817</v>
+        <v>-2.731592962040816</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1544910442830021</v>
+        <v>0.1577847122915779</v>
       </c>
       <c r="T68">
-        <v>2.178566334178821</v>
+        <v>2.244583495820603</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02222158048809138</v>
+        <v>0.02188991510767211</v>
       </c>
       <c r="W68">
-        <v>0.230560151320908</v>
+        <v>0.2306383580176109</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2222158048809139</v>
+        <v>0.2188991510767212</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.20659665492802</v>
+        <v>0.2084966549280201</v>
       </c>
       <c r="C69">
-        <v>-13.4684306630314</v>
+        <v>-14.27926532769118</v>
       </c>
       <c r="D69">
-        <v>25.4215693369686</v>
+        <v>25.19973467230881</v>
       </c>
       <c r="E69">
-        <v>26.363</v>
+        <v>26.952</v>
       </c>
       <c r="F69">
-        <v>39.463</v>
+        <v>40.052</v>
       </c>
       <c r="G69">
         <v>0.573</v>
@@ -6927,37 +6927,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M69">
-        <v>9.305375400000001</v>
+        <v>9.444261600000001</v>
       </c>
       <c r="N69">
-        <v>-7.268436624489796</v>
+        <v>-7.407322824489796</v>
       </c>
       <c r="O69">
-        <v>-0.7268436624489797</v>
+        <v>-0.7407322824489797</v>
       </c>
       <c r="P69">
-        <v>-6.541592962040816</v>
+        <v>-6.666590542040817</v>
       </c>
       <c r="Q69">
-        <v>-2.731592962040816</v>
+        <v>-2.856590542040817</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1577847122915779</v>
+        <v>0.1612842345506897</v>
       </c>
       <c r="T69">
-        <v>2.244583495820603</v>
+        <v>2.314726730064997</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02188991510767211</v>
+        <v>0.02156800459138282</v>
       </c>
       <c r="W69">
-        <v>0.2306383580176109</v>
+        <v>0.2307142645173519</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2188991510767212</v>
+        <v>0.2156800459138282</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2084966549280201</v>
+        <v>0.21039665492802</v>
       </c>
       <c r="C70">
-        <v>-14.27926532769118</v>
+        <v>-15.08626192011676</v>
       </c>
       <c r="D70">
-        <v>25.19973467230881</v>
+        <v>24.98173807988324</v>
       </c>
       <c r="E70">
-        <v>26.952</v>
+        <v>27.541</v>
       </c>
       <c r="F70">
-        <v>40.052</v>
+        <v>40.64100000000001</v>
       </c>
       <c r="G70">
         <v>0.573</v>
@@ -7009,37 +7009,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M70">
-        <v>9.444261600000001</v>
+        <v>9.583147800000001</v>
       </c>
       <c r="N70">
-        <v>-7.407322824489796</v>
+        <v>-7.546209024489796</v>
       </c>
       <c r="O70">
-        <v>-0.7407322824489797</v>
+        <v>-0.7546209024489796</v>
       </c>
       <c r="P70">
-        <v>-6.666590542040817</v>
+        <v>-6.791588122040817</v>
       </c>
       <c r="Q70">
-        <v>-2.856590542040817</v>
+        <v>-2.981588122040816</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1612842345506897</v>
+        <v>0.1650095324394217</v>
       </c>
       <c r="T70">
-        <v>2.314726730064997</v>
+        <v>2.389395334260642</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02156800459138282</v>
+        <v>0.02125542481469611</v>
       </c>
       <c r="W70">
-        <v>0.2307142645173519</v>
+        <v>0.2307879708286947</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2156800459138282</v>
+        <v>0.2125542481469611</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.21039665492802</v>
+        <v>0.2122966549280201</v>
       </c>
       <c r="C71">
-        <v>-15.08626192011676</v>
+        <v>-15.88951919263103</v>
       </c>
       <c r="D71">
-        <v>24.98173807988324</v>
+        <v>24.76748080736898</v>
       </c>
       <c r="E71">
-        <v>27.541</v>
+        <v>28.13</v>
       </c>
       <c r="F71">
-        <v>40.64100000000001</v>
+        <v>41.23</v>
       </c>
       <c r="G71">
         <v>0.573</v>
@@ -7091,37 +7091,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M71">
-        <v>9.583147800000001</v>
+        <v>9.722034000000001</v>
       </c>
       <c r="N71">
-        <v>-7.546209024489796</v>
+        <v>-7.685095224489796</v>
       </c>
       <c r="O71">
-        <v>-0.7546209024489796</v>
+        <v>-0.7685095224489796</v>
       </c>
       <c r="P71">
-        <v>-6.791588122040817</v>
+        <v>-6.916585702040816</v>
       </c>
       <c r="Q71">
-        <v>-2.981588122040816</v>
+        <v>-3.106585702040816</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1650095324394217</v>
+        <v>0.1689831835207357</v>
       </c>
       <c r="T71">
-        <v>2.389395334260642</v>
+        <v>2.469041845402664</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02125542481469611</v>
+        <v>0.02095177588877188</v>
       </c>
       <c r="W71">
-        <v>0.2307879708286947</v>
+        <v>0.2308595712454276</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2125542481469611</v>
+        <v>0.2095177588877188</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2122966549280201</v>
+        <v>0.21419665492802</v>
       </c>
       <c r="C72">
-        <v>-15.88951919263103</v>
+        <v>-16.68913253854639</v>
       </c>
       <c r="D72">
-        <v>24.76748080736898</v>
+        <v>24.55686746145361</v>
       </c>
       <c r="E72">
-        <v>28.13</v>
+        <v>28.719</v>
       </c>
       <c r="F72">
-        <v>41.23</v>
+        <v>41.819</v>
       </c>
       <c r="G72">
         <v>0.573</v>
@@ -7173,37 +7173,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M72">
-        <v>9.722034000000001</v>
+        <v>9.860920200000001</v>
       </c>
       <c r="N72">
-        <v>-7.685095224489796</v>
+        <v>-7.823981424489796</v>
       </c>
       <c r="O72">
-        <v>-0.7685095224489796</v>
+        <v>-0.7823981424489796</v>
       </c>
       <c r="P72">
-        <v>-6.916585702040816</v>
+        <v>-7.041583282040817</v>
       </c>
       <c r="Q72">
-        <v>-3.106585702040816</v>
+        <v>-3.231583282040817</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1689831835207357</v>
+        <v>0.1732308795042094</v>
       </c>
       <c r="T72">
-        <v>2.469041845402664</v>
+        <v>2.554181219382066</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02095177588877188</v>
+        <v>0.02065668045371875</v>
       </c>
       <c r="W72">
-        <v>0.2308595712454276</v>
+        <v>0.2309291547490131</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2095177588877188</v>
+        <v>0.2065668045371876</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.21419665492802</v>
+        <v>0.21609665492802</v>
       </c>
       <c r="C73">
-        <v>-16.68913253854639</v>
+        <v>-17.4851941337793</v>
       </c>
       <c r="D73">
-        <v>24.55686746145361</v>
+        <v>24.3498058662207</v>
       </c>
       <c r="E73">
-        <v>28.71899999999999</v>
+        <v>29.30799999999999</v>
       </c>
       <c r="F73">
-        <v>41.819</v>
+        <v>42.40799999999999</v>
       </c>
       <c r="G73">
         <v>0.573</v>
@@ -7255,37 +7255,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M73">
-        <v>9.860920199999999</v>
+        <v>9.999806399999999</v>
       </c>
       <c r="N73">
-        <v>-7.823981424489794</v>
+        <v>-7.962867624489794</v>
       </c>
       <c r="O73">
-        <v>-0.7823981424489794</v>
+        <v>-0.7962867624489794</v>
       </c>
       <c r="P73">
-        <v>-7.041583282040815</v>
+        <v>-7.166580862040814</v>
       </c>
       <c r="Q73">
-        <v>-3.231583282040815</v>
+        <v>-3.356580862040814</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1732308795042093</v>
+        <v>0.1777819823436454</v>
       </c>
       <c r="T73">
-        <v>2.554181219382065</v>
+        <v>2.645401977217139</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02065668045371876</v>
+        <v>0.02036978211408377</v>
       </c>
       <c r="W73">
-        <v>0.2309291547490131</v>
+        <v>0.2309968053774991</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2065668045371876</v>
+        <v>0.2036978211408378</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.21609665492802</v>
+        <v>0.21799665492802</v>
       </c>
       <c r="C74">
-        <v>-17.4851941337793</v>
+        <v>-18.27779307136024</v>
       </c>
       <c r="D74">
-        <v>24.3498058662207</v>
+        <v>24.14620692863976</v>
       </c>
       <c r="E74">
-        <v>29.30799999999999</v>
+        <v>29.897</v>
       </c>
       <c r="F74">
-        <v>42.40799999999999</v>
+        <v>42.997</v>
       </c>
       <c r="G74">
         <v>0.573</v>
@@ -7337,37 +7337,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M74">
-        <v>9.999806399999999</v>
+        <v>10.1386926</v>
       </c>
       <c r="N74">
-        <v>-7.962867624489794</v>
+        <v>-8.101753824489796</v>
       </c>
       <c r="O74">
-        <v>-0.7962867624489794</v>
+        <v>-0.8101753824489797</v>
       </c>
       <c r="P74">
-        <v>-7.166580862040814</v>
+        <v>-7.291578442040816</v>
       </c>
       <c r="Q74">
-        <v>-3.356580862040814</v>
+        <v>-3.481578442040816</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1777819823436454</v>
+        <v>0.1826702039119285</v>
       </c>
       <c r="T74">
-        <v>2.645401977217139</v>
+        <v>2.743379828225181</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02036978211408377</v>
+        <v>0.02009074400293194</v>
       </c>
       <c r="W74">
-        <v>0.2309968053774991</v>
+        <v>0.2310626025641087</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2036978211408378</v>
+        <v>0.2009074400293194</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.21799665492802</v>
+        <v>0.21989665492802</v>
       </c>
       <c r="C75">
-        <v>-18.27779307136024</v>
+        <v>-19.06701548925154</v>
       </c>
       <c r="D75">
-        <v>24.14620692863976</v>
+        <v>23.94598451074846</v>
       </c>
       <c r="E75">
-        <v>29.897</v>
+        <v>30.486</v>
       </c>
       <c r="F75">
-        <v>42.997</v>
+        <v>43.586</v>
       </c>
       <c r="G75">
         <v>0.573</v>
@@ -7419,37 +7419,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M75">
-        <v>10.1386926</v>
+        <v>10.2775788</v>
       </c>
       <c r="N75">
-        <v>-8.101753824489796</v>
+        <v>-8.240640024489796</v>
       </c>
       <c r="O75">
-        <v>-0.8101753824489797</v>
+        <v>-0.8240640024489796</v>
       </c>
       <c r="P75">
-        <v>-7.291578442040816</v>
+        <v>-7.416576022040816</v>
       </c>
       <c r="Q75">
-        <v>-3.481578442040816</v>
+        <v>-3.606576022040816</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1826702039119285</v>
+        <v>0.1879344425239258</v>
       </c>
       <c r="T75">
-        <v>2.743379828225181</v>
+        <v>2.848894437003072</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02009074400293194</v>
+        <v>0.01981924746235178</v>
       </c>
       <c r="W75">
-        <v>0.2310626025641087</v>
+        <v>0.2311266214483775</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2009074400293194</v>
+        <v>0.1981924746235177</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.21989665492802</v>
+        <v>0.22179665492802</v>
       </c>
       <c r="C76">
-        <v>-19.06701548925154</v>
+        <v>-19.8529446918581</v>
       </c>
       <c r="D76">
-        <v>23.94598451074846</v>
+        <v>23.7490553081419</v>
       </c>
       <c r="E76">
-        <v>30.486</v>
+        <v>31.075</v>
       </c>
       <c r="F76">
-        <v>43.586</v>
+        <v>44.175</v>
       </c>
       <c r="G76">
         <v>0.573</v>
@@ -7501,37 +7501,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M76">
-        <v>10.2775788</v>
+        <v>10.416465</v>
       </c>
       <c r="N76">
-        <v>-8.240640024489796</v>
+        <v>-8.379526224489796</v>
       </c>
       <c r="O76">
-        <v>-0.8240640024489796</v>
+        <v>-0.8379526224489796</v>
       </c>
       <c r="P76">
-        <v>-7.416576022040816</v>
+        <v>-7.541573602040816</v>
       </c>
       <c r="Q76">
-        <v>-3.606576022040816</v>
+        <v>-3.731573602040816</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1879344425239258</v>
+        <v>0.1936198202248828</v>
       </c>
       <c r="T76">
-        <v>2.848894437003072</v>
+        <v>2.962850214483196</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01981924746235178</v>
+        <v>0.01955499082952042</v>
       </c>
       <c r="W76">
-        <v>0.2311266214483775</v>
+        <v>0.2311889331623991</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1981924746235177</v>
+        <v>0.1955499082952042</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.22179665492802</v>
+        <v>0.22369665492802</v>
       </c>
       <c r="C77">
-        <v>-19.8529446918581</v>
+        <v>-20.63566126559147</v>
       </c>
       <c r="D77">
-        <v>23.7490553081419</v>
+        <v>23.55533873440853</v>
       </c>
       <c r="E77">
-        <v>31.075</v>
+        <v>31.664</v>
       </c>
       <c r="F77">
-        <v>44.175</v>
+        <v>44.764</v>
       </c>
       <c r="G77">
         <v>0.573</v>
@@ -7583,37 +7583,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M77">
-        <v>10.416465</v>
+        <v>10.5553512</v>
       </c>
       <c r="N77">
-        <v>-8.379526224489796</v>
+        <v>-8.518412424489796</v>
       </c>
       <c r="O77">
-        <v>-0.8379526224489796</v>
+        <v>-0.8518412424489796</v>
       </c>
       <c r="P77">
-        <v>-7.541573602040816</v>
+        <v>-7.666571182040816</v>
       </c>
       <c r="Q77">
-        <v>-3.731573602040816</v>
+        <v>-3.856571182040816</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1936198202248828</v>
+        <v>0.1997789794009196</v>
       </c>
       <c r="T77">
-        <v>2.962850214483196</v>
+        <v>3.086302306753329</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01955499082952042</v>
+        <v>0.01929768831860568</v>
       </c>
       <c r="W77">
-        <v>0.2311889331623991</v>
+        <v>0.2312496050944728</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1955499082952042</v>
+        <v>0.1929768831860568</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.22369665492802</v>
+        <v>0.22559665492802</v>
       </c>
       <c r="C78">
-        <v>-20.63566126559147</v>
+        <v>-21.41524318882372</v>
       </c>
       <c r="D78">
-        <v>23.55533873440853</v>
+        <v>23.36475681117628</v>
       </c>
       <c r="E78">
-        <v>31.664</v>
+        <v>32.253</v>
       </c>
       <c r="F78">
-        <v>44.764</v>
+        <v>45.353</v>
       </c>
       <c r="G78">
         <v>0.573</v>
@@ -7665,37 +7665,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M78">
-        <v>10.5553512</v>
+        <v>10.6942374</v>
       </c>
       <c r="N78">
-        <v>-8.518412424489796</v>
+        <v>-8.657298624489796</v>
       </c>
       <c r="O78">
-        <v>-0.8518412424489796</v>
+        <v>-0.8657298624489796</v>
       </c>
       <c r="P78">
-        <v>-7.666571182040816</v>
+        <v>-7.791568762040816</v>
       </c>
       <c r="Q78">
-        <v>-3.856571182040816</v>
+        <v>-3.981568762040816</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1997789794009196</v>
+        <v>0.2064737176357422</v>
       </c>
       <c r="T78">
-        <v>3.086302306753329</v>
+        <v>3.220489363568691</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01929768831860568</v>
+        <v>0.01904706898979262</v>
       </c>
       <c r="W78">
-        <v>0.2312496050944728</v>
+        <v>0.2313087011322069</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1929768831860568</v>
+        <v>0.1904706898979261</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.22559665492802</v>
+        <v>0.22749665492802</v>
       </c>
       <c r="C79">
-        <v>-21.41524318882372</v>
+        <v>-22.19176593654648</v>
       </c>
       <c r="D79">
-        <v>23.36475681117628</v>
+        <v>23.17723406345352</v>
       </c>
       <c r="E79">
-        <v>32.253</v>
+        <v>32.842</v>
       </c>
       <c r="F79">
-        <v>45.353</v>
+        <v>45.942</v>
       </c>
       <c r="G79">
         <v>0.573</v>
@@ -7747,37 +7747,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M79">
-        <v>10.6942374</v>
+        <v>10.8331236</v>
       </c>
       <c r="N79">
-        <v>-8.657298624489796</v>
+        <v>-8.796184824489796</v>
       </c>
       <c r="O79">
-        <v>-0.8657298624489796</v>
+        <v>-0.8796184824489797</v>
       </c>
       <c r="P79">
-        <v>-7.791568762040816</v>
+        <v>-7.916566342040817</v>
       </c>
       <c r="Q79">
-        <v>-3.981568762040816</v>
+        <v>-4.106566342040816</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2064737176357422</v>
+        <v>0.2137770684373669</v>
       </c>
       <c r="T79">
-        <v>3.220489363568691</v>
+        <v>3.366875243730905</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01904706898979262</v>
+        <v>0.01880287579761579</v>
       </c>
       <c r="W79">
-        <v>0.2313087011322069</v>
+        <v>0.2313662818869222</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1904706898979261</v>
+        <v>0.1880287579761579</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.22749665492802</v>
+        <v>0.22939665492802</v>
       </c>
       <c r="C80">
-        <v>-22.19176593654648</v>
+        <v>-22.96530258003033</v>
       </c>
       <c r="D80">
-        <v>23.17723406345352</v>
+        <v>22.99269741996967</v>
       </c>
       <c r="E80">
-        <v>32.842</v>
+        <v>33.431</v>
       </c>
       <c r="F80">
-        <v>45.942</v>
+        <v>46.531</v>
       </c>
       <c r="G80">
         <v>0.573</v>
@@ -7829,37 +7829,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M80">
-        <v>10.8331236</v>
+        <v>10.9720098</v>
       </c>
       <c r="N80">
-        <v>-8.796184824489796</v>
+        <v>-8.935071024489796</v>
       </c>
       <c r="O80">
-        <v>-0.8796184824489797</v>
+        <v>-0.8935071024489796</v>
       </c>
       <c r="P80">
-        <v>-7.916566342040817</v>
+        <v>-8.041563922040815</v>
       </c>
       <c r="Q80">
-        <v>-4.106566342040816</v>
+        <v>-4.231563922040815</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2137770684373669</v>
+        <v>0.2217759764581938</v>
       </c>
       <c r="T80">
-        <v>3.366875243730905</v>
+        <v>3.527202636289519</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01880287579761579</v>
+        <v>0.01856486471157002</v>
       </c>
       <c r="W80">
-        <v>0.2313662818869222</v>
+        <v>0.2314224049010118</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1880287579761579</v>
+        <v>0.1856486471157002</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.22939665492802</v>
+        <v>0.23129665492802</v>
       </c>
       <c r="C81">
-        <v>-22.96530258003033</v>
+        <v>-23.73592388176073</v>
       </c>
       <c r="D81">
-        <v>22.99269741996967</v>
+        <v>22.81107611823927</v>
       </c>
       <c r="E81">
-        <v>33.431</v>
+        <v>34.02</v>
       </c>
       <c r="F81">
-        <v>46.531</v>
+        <v>47.12</v>
       </c>
       <c r="G81">
         <v>0.573</v>
@@ -7911,37 +7911,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M81">
-        <v>10.9720098</v>
+        <v>11.110896</v>
       </c>
       <c r="N81">
-        <v>-8.935071024489796</v>
+        <v>-9.073957224489797</v>
       </c>
       <c r="O81">
-        <v>-0.8935071024489796</v>
+        <v>-0.9073957224489798</v>
       </c>
       <c r="P81">
-        <v>-8.041563922040815</v>
+        <v>-8.166561502040818</v>
       </c>
       <c r="Q81">
-        <v>-4.231563922040815</v>
+        <v>-4.356561502040817</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2217759764581938</v>
+        <v>0.2305747752811036</v>
       </c>
       <c r="T81">
-        <v>3.527202636289519</v>
+        <v>3.703562768103995</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01856486471157002</v>
+        <v>0.01833280390267539</v>
       </c>
       <c r="W81">
-        <v>0.2314224049010118</v>
+        <v>0.2314771248397491</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1856486471157002</v>
+        <v>0.183328039026754</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.23129665492802</v>
+        <v>0.2331966549280201</v>
       </c>
       <c r="C82">
-        <v>-23.73592388176073</v>
+        <v>-24.50369838590986</v>
       </c>
       <c r="D82">
-        <v>22.81107611823927</v>
+        <v>22.63230161409015</v>
       </c>
       <c r="E82">
-        <v>34.02</v>
+        <v>34.609</v>
       </c>
       <c r="F82">
-        <v>47.12</v>
+        <v>47.709</v>
       </c>
       <c r="G82">
         <v>0.573</v>
@@ -7993,37 +7993,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M82">
-        <v>11.110896</v>
+        <v>11.2497822</v>
       </c>
       <c r="N82">
-        <v>-9.073957224489797</v>
+        <v>-9.212843424489797</v>
       </c>
       <c r="O82">
-        <v>-0.9073957224489798</v>
+        <v>-0.9212843424489798</v>
       </c>
       <c r="P82">
-        <v>-8.166561502040818</v>
+        <v>-8.291559082040818</v>
       </c>
       <c r="Q82">
-        <v>-4.356561502040817</v>
+        <v>-4.481559082040818</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2305747752811036</v>
+        <v>0.2402997634537933</v>
       </c>
       <c r="T82">
-        <v>3.703562768103995</v>
+        <v>3.898487124319995</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01833280390267539</v>
+        <v>0.01810647299029668</v>
       </c>
       <c r="W82">
-        <v>0.2314771248397491</v>
+        <v>0.2315304936688881</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.183328039026754</v>
+        <v>0.1810647299029668</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2331966549280201</v>
+        <v>0.2350966549280201</v>
       </c>
       <c r="C83">
-        <v>-24.50369838590986</v>
+        <v>-25.26869250458726</v>
       </c>
       <c r="D83">
-        <v>22.63230161409015</v>
+        <v>22.45630749541274</v>
       </c>
       <c r="E83">
-        <v>34.609</v>
+        <v>35.198</v>
       </c>
       <c r="F83">
-        <v>47.709</v>
+        <v>48.298</v>
       </c>
       <c r="G83">
         <v>0.573</v>
@@ -8075,37 +8075,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M83">
-        <v>11.2497822</v>
+        <v>11.3886684</v>
       </c>
       <c r="N83">
-        <v>-9.212843424489797</v>
+        <v>-9.351729624489796</v>
       </c>
       <c r="O83">
-        <v>-0.9212843424489798</v>
+        <v>-0.9351729624489796</v>
       </c>
       <c r="P83">
-        <v>-8.291559082040818</v>
+        <v>-8.416556662040817</v>
       </c>
       <c r="Q83">
-        <v>-4.481559082040818</v>
+        <v>-4.606556662040816</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2402997634537933</v>
+        <v>0.2511053058678928</v>
       </c>
       <c r="T83">
-        <v>3.898487124319995</v>
+        <v>4.115069742337773</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01810647299029668</v>
+        <v>0.01788566234407355</v>
       </c>
       <c r="W83">
-        <v>0.2315304936688881</v>
+        <v>0.2315825608192675</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1810647299029668</v>
+        <v>0.1788566234407356</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2350966549280201</v>
+        <v>0.23699665492802</v>
       </c>
       <c r="C84">
-        <v>-25.26869250458726</v>
+        <v>-26.03097060009731</v>
       </c>
       <c r="D84">
-        <v>22.45630749541274</v>
+        <v>22.28302939990269</v>
       </c>
       <c r="E84">
-        <v>35.198</v>
+        <v>35.787</v>
       </c>
       <c r="F84">
-        <v>48.298</v>
+        <v>48.887</v>
       </c>
       <c r="G84">
         <v>0.573</v>
@@ -8157,37 +8157,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M84">
-        <v>11.3886684</v>
+        <v>11.5275546</v>
       </c>
       <c r="N84">
-        <v>-9.351729624489796</v>
+        <v>-9.490615824489796</v>
       </c>
       <c r="O84">
-        <v>-0.9351729624489796</v>
+        <v>-0.9490615824489796</v>
       </c>
       <c r="P84">
-        <v>-8.416556662040817</v>
+        <v>-8.541554242040815</v>
       </c>
       <c r="Q84">
-        <v>-4.606556662040816</v>
+        <v>-4.731554242040815</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2511053058678928</v>
+        <v>0.2631820885660042</v>
       </c>
       <c r="T84">
-        <v>4.115069742337773</v>
+        <v>4.357132668357642</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01788566234407355</v>
+        <v>0.01767017243631363</v>
       </c>
       <c r="W84">
-        <v>0.2315825608192675</v>
+        <v>0.2316333733395173</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1788566234407356</v>
+        <v>0.1767017243631364</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.23699665492802</v>
+        <v>0.23889665492802</v>
       </c>
       <c r="C85">
-        <v>-26.03097060009731</v>
+        <v>-26.79059506341751</v>
       </c>
       <c r="D85">
-        <v>22.28302939990269</v>
+        <v>22.1124049365825</v>
       </c>
       <c r="E85">
-        <v>35.787</v>
+        <v>36.376</v>
       </c>
       <c r="F85">
-        <v>48.887</v>
+        <v>49.47600000000001</v>
       </c>
       <c r="G85">
         <v>0.573</v>
@@ -8239,37 +8239,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M85">
-        <v>11.5275546</v>
+        <v>11.6664408</v>
       </c>
       <c r="N85">
-        <v>-9.490615824489796</v>
+        <v>-9.629502024489797</v>
       </c>
       <c r="O85">
-        <v>-0.9490615824489796</v>
+        <v>-0.9629502024489798</v>
       </c>
       <c r="P85">
-        <v>-8.541554242040815</v>
+        <v>-8.666551822040818</v>
       </c>
       <c r="Q85">
-        <v>-4.731554242040815</v>
+        <v>-4.856551822040817</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2631820885660042</v>
+        <v>0.2767684691013795</v>
       </c>
       <c r="T85">
-        <v>4.357132668357642</v>
+        <v>4.629453460129995</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01767017243631363</v>
+        <v>0.01745981324064323</v>
       </c>
       <c r="W85">
-        <v>0.2316333733395173</v>
+        <v>0.2316829760378563</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1767017243631364</v>
+        <v>0.1745981324064323</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.23889665492802</v>
+        <v>0.24079665492802</v>
       </c>
       <c r="C86">
-        <v>-26.79059506341749</v>
+        <v>-27.54762638909865</v>
       </c>
       <c r="D86">
-        <v>22.1124049365825</v>
+        <v>21.94437361090135</v>
       </c>
       <c r="E86">
-        <v>36.376</v>
+        <v>36.965</v>
       </c>
       <c r="F86">
-        <v>49.476</v>
+        <v>50.065</v>
       </c>
       <c r="G86">
         <v>0.573</v>
@@ -8321,37 +8321,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M86">
-        <v>11.6664408</v>
+        <v>11.805327</v>
       </c>
       <c r="N86">
-        <v>-9.629502024489796</v>
+        <v>-9.768388224489795</v>
       </c>
       <c r="O86">
-        <v>-0.9629502024489796</v>
+        <v>-0.9768388224489796</v>
       </c>
       <c r="P86">
-        <v>-8.666551822040816</v>
+        <v>-8.791549402040816</v>
       </c>
       <c r="Q86">
-        <v>-4.856551822040815</v>
+        <v>-4.981549402040816</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2767684691013794</v>
+        <v>0.2921663670414713</v>
       </c>
       <c r="T86">
-        <v>4.629453460129993</v>
+        <v>4.938083690805326</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01745981324064323</v>
+        <v>0.01725440367310625</v>
       </c>
       <c r="W86">
-        <v>0.2316829760378563</v>
+        <v>0.2317314116138816</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1745981324064324</v>
+        <v>0.1725440367310626</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.24079665492802</v>
+        <v>0.24269665492802</v>
       </c>
       <c r="C87">
-        <v>-27.54762638909865</v>
+        <v>-28.30212324677587</v>
       </c>
       <c r="D87">
-        <v>21.94437361090135</v>
+        <v>21.77887675322412</v>
       </c>
       <c r="E87">
-        <v>36.965</v>
+        <v>37.55399999999999</v>
       </c>
       <c r="F87">
-        <v>50.065</v>
+        <v>50.654</v>
       </c>
       <c r="G87">
         <v>0.573</v>
@@ -8403,37 +8403,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M87">
-        <v>11.805327</v>
+        <v>11.9442132</v>
       </c>
       <c r="N87">
-        <v>-9.768388224489795</v>
+        <v>-9.907274424489795</v>
       </c>
       <c r="O87">
-        <v>-0.9768388224489796</v>
+        <v>-0.9907274424489796</v>
       </c>
       <c r="P87">
-        <v>-8.791549402040816</v>
+        <v>-8.916546982040815</v>
       </c>
       <c r="Q87">
-        <v>-4.981549402040816</v>
+        <v>-5.106546982040815</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2921663670414713</v>
+        <v>0.3097639646872907</v>
       </c>
       <c r="T87">
-        <v>4.938083690805326</v>
+        <v>5.290803954434278</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01725440367310625</v>
+        <v>0.01705377107225618</v>
       </c>
       <c r="W87">
-        <v>0.2317314116138816</v>
+        <v>0.231778720781162</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1725440367310626</v>
+        <v>0.1705377107225619</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.24269665492802</v>
+        <v>0.24459665492802</v>
       </c>
       <c r="C88">
-        <v>-28.30212324677587</v>
+        <v>-29.05414254946788</v>
       </c>
       <c r="D88">
-        <v>21.77887675322412</v>
+        <v>21.61585745053212</v>
       </c>
       <c r="E88">
-        <v>37.55399999999999</v>
+        <v>38.14299999999999</v>
       </c>
       <c r="F88">
-        <v>50.654</v>
+        <v>51.24299999999999</v>
       </c>
       <c r="G88">
         <v>0.573</v>
@@ -8485,37 +8485,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M88">
-        <v>11.9442132</v>
+        <v>12.0830994</v>
       </c>
       <c r="N88">
-        <v>-9.907274424489795</v>
+        <v>-10.0461606244898</v>
       </c>
       <c r="O88">
-        <v>-0.9907274424489796</v>
+        <v>-1.004616062448979</v>
       </c>
       <c r="P88">
-        <v>-8.916546982040815</v>
+        <v>-9.041544562040816</v>
       </c>
       <c r="Q88">
-        <v>-5.106546982040815</v>
+        <v>-5.231544562040815</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3097639646872907</v>
+        <v>0.3300688850478515</v>
       </c>
       <c r="T88">
-        <v>5.290803954434278</v>
+        <v>5.697788874006145</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01705377107225618</v>
+        <v>0.01685775071510381</v>
       </c>
       <c r="W88">
-        <v>0.231778720781162</v>
+        <v>0.2318249423813785</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1705377107225619</v>
+        <v>0.1685775071510381</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.24459665492802</v>
+        <v>0.24649665492802</v>
       </c>
       <c r="C89">
-        <v>-29.05414254946788</v>
+        <v>-29.80373951883168</v>
       </c>
       <c r="D89">
-        <v>21.61585745053212</v>
+        <v>21.45526048116832</v>
       </c>
       <c r="E89">
-        <v>38.14299999999999</v>
+        <v>38.732</v>
       </c>
       <c r="F89">
-        <v>51.24299999999999</v>
+        <v>51.832</v>
       </c>
       <c r="G89">
         <v>0.573</v>
@@ -8567,37 +8567,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M89">
-        <v>12.0830994</v>
+        <v>12.2219856</v>
       </c>
       <c r="N89">
-        <v>-10.0461606244898</v>
+        <v>-10.1850468244898</v>
       </c>
       <c r="O89">
-        <v>-1.004616062448979</v>
+        <v>-1.01850468244898</v>
       </c>
       <c r="P89">
-        <v>-9.041544562040816</v>
+        <v>-9.166542142040816</v>
       </c>
       <c r="Q89">
-        <v>-5.231544562040815</v>
+        <v>-5.356542142040816</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3300688850478515</v>
+        <v>0.3537579588018392</v>
       </c>
       <c r="T89">
-        <v>5.697788874006145</v>
+        <v>6.172604613506658</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01685775071510381</v>
+        <v>0.01666618536606854</v>
       </c>
       <c r="W89">
-        <v>0.2318249423813785</v>
+        <v>0.231870113490681</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1685775071510381</v>
+        <v>0.1666618536606854</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.24649665492802</v>
+        <v>0.24839665492802</v>
       </c>
       <c r="C90">
-        <v>-29.80373951883168</v>
+        <v>-30.55096774752984</v>
       </c>
       <c r="D90">
-        <v>21.45526048116832</v>
+        <v>21.29703225247016</v>
       </c>
       <c r="E90">
-        <v>38.732</v>
+        <v>39.321</v>
       </c>
       <c r="F90">
-        <v>51.832</v>
+        <v>52.421</v>
       </c>
       <c r="G90">
         <v>0.573</v>
@@ -8649,37 +8649,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M90">
-        <v>12.2219856</v>
+        <v>12.3608718</v>
       </c>
       <c r="N90">
-        <v>-10.1850468244898</v>
+        <v>-10.3239330244898</v>
       </c>
       <c r="O90">
-        <v>-1.01850468244898</v>
+        <v>-1.03239330244898</v>
       </c>
       <c r="P90">
-        <v>-9.166542142040816</v>
+        <v>-9.291539722040817</v>
       </c>
       <c r="Q90">
-        <v>-5.356542142040816</v>
+        <v>-5.481539722040816</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3537579588018392</v>
+        <v>0.3817541368747338</v>
       </c>
       <c r="T90">
-        <v>6.172604613506658</v>
+        <v>6.73375048746181</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01666618536606854</v>
+        <v>0.01647892485633743</v>
       </c>
       <c r="W90">
-        <v>0.231870113490681</v>
+        <v>0.2319142695188756</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1666618536606854</v>
+        <v>0.1647892485633744</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.24839665492802</v>
+        <v>0.25029665492802</v>
       </c>
       <c r="C91">
-        <v>-30.55096774752984</v>
+        <v>-31.2958792588583</v>
       </c>
       <c r="D91">
-        <v>21.29703225247016</v>
+        <v>21.1411207411417</v>
       </c>
       <c r="E91">
-        <v>39.321</v>
+        <v>39.91</v>
       </c>
       <c r="F91">
-        <v>52.421</v>
+        <v>53.01</v>
       </c>
       <c r="G91">
         <v>0.573</v>
@@ -8731,37 +8731,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M91">
-        <v>12.3608718</v>
+        <v>12.499758</v>
       </c>
       <c r="N91">
-        <v>-10.3239330244898</v>
+        <v>-10.4628192244898</v>
       </c>
       <c r="O91">
-        <v>-1.03239330244898</v>
+        <v>-1.04628192244898</v>
       </c>
       <c r="P91">
-        <v>-9.291539722040817</v>
+        <v>-9.416537302040815</v>
       </c>
       <c r="Q91">
-        <v>-5.481539722040816</v>
+        <v>-5.606537302040815</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3817541368747338</v>
+        <v>0.4153495505622071</v>
       </c>
       <c r="T91">
-        <v>6.73375048746181</v>
+        <v>7.407125536207991</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01647892485633743</v>
+        <v>0.01629582569126702</v>
       </c>
       <c r="W91">
-        <v>0.2319142695188756</v>
+        <v>0.2319574443019992</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1647892485633744</v>
+        <v>0.1629582569126702</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.25029665492802</v>
+        <v>0.2521966549280201</v>
       </c>
       <c r="C92">
-        <v>-31.2958792588583</v>
+        <v>-32.03852456377405</v>
       </c>
       <c r="D92">
-        <v>21.1411207411417</v>
+        <v>20.98747543622596</v>
       </c>
       <c r="E92">
-        <v>39.91</v>
+        <v>40.499</v>
       </c>
       <c r="F92">
-        <v>53.01</v>
+        <v>53.599</v>
       </c>
       <c r="G92">
         <v>0.573</v>
@@ -8813,37 +8813,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M92">
-        <v>12.499758</v>
+        <v>12.6386442</v>
       </c>
       <c r="N92">
-        <v>-10.4628192244898</v>
+        <v>-10.6017054244898</v>
       </c>
       <c r="O92">
-        <v>-1.04628192244898</v>
+        <v>-1.06017054244898</v>
       </c>
       <c r="P92">
-        <v>-9.416537302040815</v>
+        <v>-9.541534882040818</v>
       </c>
       <c r="Q92">
-        <v>-5.606537302040815</v>
+        <v>-5.731534882040817</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4153495505622071</v>
+        <v>0.4564106117357857</v>
       </c>
       <c r="T92">
-        <v>7.407125536207991</v>
+        <v>8.230139484675545</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01629582569126702</v>
+        <v>0.01611675068367067</v>
       </c>
       <c r="W92">
-        <v>0.2319574443019992</v>
+        <v>0.2319996701887905</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1629582569126702</v>
+        <v>0.1611675068367068</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2521966549280201</v>
+        <v>0.25409665492802</v>
       </c>
       <c r="C93">
-        <v>-32.03852456377405</v>
+        <v>-32.77895271545394</v>
       </c>
       <c r="D93">
-        <v>20.98747543622596</v>
+        <v>20.83604728454607</v>
       </c>
       <c r="E93">
-        <v>40.499</v>
+        <v>41.088</v>
       </c>
       <c r="F93">
-        <v>53.599</v>
+        <v>54.188</v>
       </c>
       <c r="G93">
         <v>0.573</v>
@@ -8895,37 +8895,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M93">
-        <v>12.6386442</v>
+        <v>12.7775304</v>
       </c>
       <c r="N93">
-        <v>-10.6017054244898</v>
+        <v>-10.7405916244898</v>
       </c>
       <c r="O93">
-        <v>-1.06017054244898</v>
+        <v>-1.07405916244898</v>
       </c>
       <c r="P93">
-        <v>-9.541534882040818</v>
+        <v>-9.666532462040816</v>
       </c>
       <c r="Q93">
-        <v>-5.731534882040817</v>
+        <v>-5.856532462040816</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4564106117357857</v>
+        <v>0.5077369382027591</v>
       </c>
       <c r="T93">
-        <v>8.230139484675545</v>
+        <v>9.258906920259992</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01611675068367067</v>
+        <v>0.01594156861102208</v>
       </c>
       <c r="W93">
-        <v>0.2319996701887905</v>
+        <v>0.232040978121521</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1611675068367068</v>
+        <v>0.1594156861102208</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.25409665492802</v>
+        <v>0.25599665492802</v>
       </c>
       <c r="C94">
-        <v>-32.77895271545394</v>
+        <v>-33.51721136150874</v>
       </c>
       <c r="D94">
-        <v>20.83604728454607</v>
+        <v>20.68678863849126</v>
       </c>
       <c r="E94">
-        <v>41.088</v>
+        <v>41.677</v>
       </c>
       <c r="F94">
-        <v>54.188</v>
+        <v>54.777</v>
       </c>
       <c r="G94">
         <v>0.573</v>
@@ -8977,37 +8977,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M94">
-        <v>12.7775304</v>
+        <v>12.9164166</v>
       </c>
       <c r="N94">
-        <v>-10.7405916244898</v>
+        <v>-10.8794778244898</v>
       </c>
       <c r="O94">
-        <v>-1.07405916244898</v>
+        <v>-1.08794778244898</v>
       </c>
       <c r="P94">
-        <v>-9.666532462040816</v>
+        <v>-9.791530042040817</v>
       </c>
       <c r="Q94">
-        <v>-5.856532462040816</v>
+        <v>-5.981530042040816</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5077369382027591</v>
+        <v>0.5737279293745817</v>
       </c>
       <c r="T94">
-        <v>9.258906920259992</v>
+        <v>10.58160790886856</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01594156861102208</v>
+        <v>0.01577015389477453</v>
       </c>
       <c r="W94">
-        <v>0.232040978121521</v>
+        <v>0.2320813977116122</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1594156861102208</v>
+        <v>0.1577015389477453</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.25599665492802</v>
+        <v>0.2578966549280201</v>
       </c>
       <c r="C95">
-        <v>-33.51721136150874</v>
+        <v>-34.25334679396868</v>
       </c>
       <c r="D95">
-        <v>20.68678863849126</v>
+        <v>20.53965320603132</v>
       </c>
       <c r="E95">
-        <v>41.677</v>
+        <v>42.266</v>
       </c>
       <c r="F95">
-        <v>54.777</v>
+        <v>55.366</v>
       </c>
       <c r="G95">
         <v>0.573</v>
@@ -9059,37 +9059,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M95">
-        <v>12.9164166</v>
+        <v>13.0553028</v>
       </c>
       <c r="N95">
-        <v>-10.8794778244898</v>
+        <v>-11.0183640244898</v>
       </c>
       <c r="O95">
-        <v>-1.08794778244898</v>
+        <v>-1.10183640244898</v>
       </c>
       <c r="P95">
-        <v>-9.791530042040817</v>
+        <v>-9.916527622040816</v>
       </c>
       <c r="Q95">
-        <v>-5.981530042040816</v>
+        <v>-6.106527622040815</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5737279293745817</v>
+        <v>0.6617159176036789</v>
       </c>
       <c r="T95">
-        <v>10.58160790886856</v>
+        <v>12.34520922701333</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01577015389477453</v>
+        <v>0.01560238630014927</v>
       </c>
       <c r="W95">
-        <v>0.2320813977116122</v>
+        <v>0.2321209573104248</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1577015389477453</v>
+        <v>0.1560238630014927</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2578966549280201</v>
+        <v>0.2597966549280201</v>
       </c>
       <c r="C96">
-        <v>-34.25334679396868</v>
+        <v>-34.98740399715108</v>
       </c>
       <c r="D96">
-        <v>20.53965320603132</v>
+        <v>20.39459600284892</v>
       </c>
       <c r="E96">
-        <v>42.266</v>
+        <v>42.855</v>
       </c>
       <c r="F96">
-        <v>55.366</v>
+        <v>55.95500000000001</v>
       </c>
       <c r="G96">
         <v>0.573</v>
@@ -9141,37 +9141,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M96">
-        <v>13.0553028</v>
+        <v>13.194189</v>
       </c>
       <c r="N96">
-        <v>-11.0183640244898</v>
+        <v>-11.1572502244898</v>
       </c>
       <c r="O96">
-        <v>-1.10183640244898</v>
+        <v>-1.11572502244898</v>
       </c>
       <c r="P96">
-        <v>-9.916527622040816</v>
+        <v>-10.04152520204082</v>
       </c>
       <c r="Q96">
-        <v>-6.106527622040815</v>
+        <v>-6.231525202040817</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6617159176036789</v>
+        <v>0.7848991011244152</v>
       </c>
       <c r="T96">
-        <v>12.34520922701333</v>
+        <v>14.814251072416</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01560238630014927</v>
+        <v>0.01543815065488454</v>
       </c>
       <c r="W96">
-        <v>0.2321209573104248</v>
+        <v>0.2321596840755782</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1560238630014927</v>
+        <v>0.1543815065488454</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2597966549280201</v>
+        <v>0.26169665492802</v>
       </c>
       <c r="C97">
-        <v>-34.98740399715108</v>
+        <v>-35.71942669351382</v>
       </c>
       <c r="D97">
-        <v>20.39459600284892</v>
+        <v>20.25157330648619</v>
       </c>
       <c r="E97">
-        <v>42.855</v>
+        <v>43.444</v>
       </c>
       <c r="F97">
-        <v>55.95500000000001</v>
+        <v>56.544</v>
       </c>
       <c r="G97">
         <v>0.573</v>
@@ -9223,37 +9223,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M97">
-        <v>13.194189</v>
+        <v>13.3330752</v>
       </c>
       <c r="N97">
-        <v>-11.1572502244898</v>
+        <v>-11.2961364244898</v>
       </c>
       <c r="O97">
-        <v>-1.11572502244898</v>
+        <v>-1.12961364244898</v>
       </c>
       <c r="P97">
-        <v>-10.04152520204082</v>
+        <v>-10.16652278204082</v>
       </c>
       <c r="Q97">
-        <v>-6.231525202040817</v>
+        <v>-6.356522782040816</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7848991011244152</v>
+        <v>0.9696738764055192</v>
       </c>
       <c r="T97">
-        <v>14.814251072416</v>
+        <v>18.51781384052001</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01543815065488454</v>
+        <v>0.01527733658556283</v>
       </c>
       <c r="W97">
-        <v>0.2321596840755782</v>
+        <v>0.2321976040331243</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1543815065488454</v>
+        <v>0.1527733658556283</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.26169665492802</v>
+        <v>0.26359665492802</v>
       </c>
       <c r="C98">
-        <v>-35.71942669351381</v>
+        <v>-36.44945738759289</v>
       </c>
       <c r="D98">
-        <v>20.25157330648619</v>
+        <v>20.1105426124071</v>
       </c>
       <c r="E98">
-        <v>43.444</v>
+        <v>44.03299999999999</v>
       </c>
       <c r="F98">
-        <v>56.544</v>
+        <v>57.133</v>
       </c>
       <c r="G98">
         <v>0.573</v>
@@ -9305,37 +9305,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M98">
-        <v>13.3330752</v>
+        <v>13.4719614</v>
       </c>
       <c r="N98">
-        <v>-11.2961364244898</v>
+        <v>-11.4350226244898</v>
       </c>
       <c r="O98">
-        <v>-1.12961364244898</v>
+        <v>-1.143502262448979</v>
       </c>
       <c r="P98">
-        <v>-10.16652278204081</v>
+        <v>-10.29152036204082</v>
       </c>
       <c r="Q98">
-        <v>-6.356522782040814</v>
+        <v>-6.481520362040815</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9696738764055167</v>
+        <v>1.277631835207356</v>
       </c>
       <c r="T98">
-        <v>18.51781384051996</v>
+        <v>24.69041845402661</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01527733658556283</v>
+        <v>0.01511983827024775</v>
       </c>
       <c r="W98">
-        <v>0.2321976040331243</v>
+        <v>0.2322347421358756</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1527733658556283</v>
+        <v>0.1511983827024775</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.26359665492802</v>
+        <v>0.26549665492802</v>
       </c>
       <c r="C99">
-        <v>-36.44945738759289</v>
+        <v>-37.17753740811681</v>
       </c>
       <c r="D99">
-        <v>20.1105426124071</v>
+        <v>19.97146259188319</v>
       </c>
       <c r="E99">
-        <v>44.03299999999999</v>
+        <v>44.62199999999999</v>
       </c>
       <c r="F99">
-        <v>57.133</v>
+        <v>57.72199999999999</v>
       </c>
       <c r="G99">
         <v>0.573</v>
@@ -9387,37 +9387,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M99">
-        <v>13.4719614</v>
+        <v>13.6108476</v>
       </c>
       <c r="N99">
-        <v>-11.4350226244898</v>
+        <v>-11.57390882448979</v>
       </c>
       <c r="O99">
-        <v>-1.143502262448979</v>
+        <v>-1.15739088244898</v>
       </c>
       <c r="P99">
-        <v>-10.29152036204082</v>
+        <v>-10.41651794204082</v>
       </c>
       <c r="Q99">
-        <v>-6.481520362040815</v>
+        <v>-6.606517942040815</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.277631835207356</v>
+        <v>1.893547752811034</v>
       </c>
       <c r="T99">
-        <v>24.69041845402661</v>
+        <v>37.03562768103991</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01511983827024775</v>
+        <v>0.01496555420626563</v>
       </c>
       <c r="W99">
-        <v>0.2322347421358756</v>
+        <v>0.2322711223181626</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1511983827024775</v>
+        <v>0.1496555420626563</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.26549665492802</v>
+        <v>0.26739665492802</v>
       </c>
       <c r="C100">
-        <v>-37.17753740811681</v>
+        <v>-37.90370694838541</v>
       </c>
       <c r="D100">
-        <v>19.97146259188319</v>
+        <v>19.83429305161459</v>
       </c>
       <c r="E100">
-        <v>44.62199999999999</v>
+        <v>45.211</v>
       </c>
       <c r="F100">
-        <v>57.72199999999999</v>
+        <v>58.311</v>
       </c>
       <c r="G100">
         <v>0.573</v>
@@ -9469,37 +9469,37 @@
         <v>2.036938775510204</v>
       </c>
       <c r="M100">
-        <v>13.6108476</v>
+        <v>13.7497338</v>
       </c>
       <c r="N100">
-        <v>-11.57390882448979</v>
+        <v>-11.7127950244898</v>
       </c>
       <c r="O100">
-        <v>-1.15739088244898</v>
+        <v>-1.17127950244898</v>
       </c>
       <c r="P100">
-        <v>-10.41651794204082</v>
+        <v>-10.54151552204082</v>
       </c>
       <c r="Q100">
-        <v>-6.606517942040815</v>
+        <v>-6.731515522040816</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.893547752811034</v>
+        <v>3.741295505622067</v>
       </c>
       <c r="T100">
-        <v>37.03562768103991</v>
+        <v>74.07125536207982</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01496555420626563</v>
+        <v>0.01481438699206093</v>
       </c>
       <c r="W100">
-        <v>0.2322711223181626</v>
+        <v>0.232306767547272</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1496555420626563</v>
+        <v>0.1481438699206092</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.26739665492802</v>
-      </c>
-      <c r="C101">
-        <v>-37.90370694838541</v>
-      </c>
-      <c r="D101">
-        <v>19.83429305161459</v>
-      </c>
-      <c r="E101">
-        <v>45.211</v>
-      </c>
-      <c r="F101">
-        <v>58.311</v>
-      </c>
-      <c r="G101">
-        <v>0.573</v>
-      </c>
-      <c r="H101">
-        <v>45.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.846938775510204</v>
-      </c>
-      <c r="K101">
-        <v>3.81</v>
-      </c>
-      <c r="L101">
-        <v>2.036938775510204</v>
-      </c>
-      <c r="M101">
-        <v>13.7497338</v>
-      </c>
-      <c r="N101">
-        <v>-11.7127950244898</v>
-      </c>
-      <c r="O101">
-        <v>-1.17127950244898</v>
-      </c>
-      <c r="P101">
-        <v>-10.54151552204082</v>
-      </c>
-      <c r="Q101">
-        <v>-6.731515522040816</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.741295505622067</v>
-      </c>
-      <c r="T101">
-        <v>74.07125536207982</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01481438699206093</v>
-      </c>
-      <c r="W101">
-        <v>0.232306767547272</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1481438699206092</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
